--- a/tools/find-a-venue/data/venues_master_seed.xlsx
+++ b/tools/find-a-venue/data/venues_master_seed.xlsx
@@ -2041,7 +2041,11 @@
           <t>Washington Heights</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr"/>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
       <c r="H11" s="15" t="n">
         <v>40.8571</v>
       </c>

--- a/tools/find-a-venue/data/venues_master_seed.xlsx
+++ b/tools/find-a-venue/data/venues_master_seed.xlsx
@@ -13,9 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Past events" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field guide" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Venues'!$A$1:$AX$53</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -23,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +59,10 @@
     <font>
       <i val="1"/>
       <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="14">
@@ -143,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -200,6 +202,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -279,17 +285,17 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Find a venue</author>
+    <author>Field guide</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Stable ID used as the URL slug. Don't change once set; leave blank for new venues and the sync script will create one.</t>
+        <t>Stable ID used as the URL slug. Don't change once set; leave blank for new venues and the sync will create one.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Only Approved venues appear on the site. New venues start as Pending review.</t>
+        <t>Only Approved venues appear on the site. New venues start as Pending review. Allowed: Approved · Pending review · Archived.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -299,7 +305,7 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>What kind of place this is.</t>
+        <t>What kind of place this is. Allowed: Park / public space · Privately owned public space (POPS) · Library · Bar / cafe / restaurant · Club / event venue · Arts / community space · Gallery / museum · Bookstore · Church / meeting house · University · Makerspace · Community tech space · Radio station / studio · Other.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
@@ -307,9 +313,14 @@
         <t>Full street address. Public business or institutional addresses only. Never a private home.</t>
       </text>
     </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Allowed: Manhattan · Brooklyn · Queens · Bronx · Staten Island.</t>
+      </text>
+    </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>Decimal degrees. The sync script can fill this from the address.</t>
+        <t>Decimal degrees. The sync can fill this from the address.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
@@ -319,140 +330,80 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>approx = pin placed by neighborhood or cross street; confirm the address to upgrade.</t>
+        <t>approx = pin placed by neighborhood or cross street; confirm the address to upgrade. Allowed: exact · approx.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Allowed: Indoor · Outdoor · Both.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Rough number of people standing. An estimate is fine; say so in notes.</t>
+        <t>Rough number of people the space holds. An estimate is fine.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Shown as 'Public / cost'. Parks, plazas and libraries also show as public spaces. Allowed: Free · Donation · Purchase / minimum spend · Rental fee · Ticketed by venue · Unknown.</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>Is there somewhere for people to sit?</t>
+        <t>Freeform. Who to ask, how far ahead, permits, any fees.</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>Useful for crafts, zines and letter writing.</t>
+        <t>Freeform and PUBLIC: a venue's events email, booking form or front desk. Never a personal email or phone; those go in the collaborator-only columns.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>Can a group have its own room or the whole venue?</t>
+        <t>Freeform. Outside food OK? Purchase required? Alcohol?</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>Outdoor venues: nearest indoor fallback, or how hosts have handled rain.</t>
+        <t>Freeform. Step-free entry, elevator, accessible restroom, seating, lighting, quiet corner.</t>
       </text>
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>Can people talk and hear each other?</t>
+        <t>Freeform. Power outlets, sound system or mic, projector or screen.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Freeform. Anything else: where to set up, what's worked, what to avoid.</t>
       </text>
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
-        <t>Has the venue been OK with phone-free rules, phone check or lockers?</t>
+        <t>Who to talk to about events, and their role.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Prefer a business or events address over a personal one.</t>
       </text>
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
-        <t>e.g. '$X minimum on weeknights', 'free for community groups'.</t>
+        <t>Business line only.</t>
       </text>
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
-        <t>How hosts have secured the space.</t>
+        <t>Who in the community knows them, past events, any history to be aware of.</t>
       </text>
     </comment>
     <comment ref="X1" authorId="0" shapeId="0">
       <text>
-        <t>Parks and plazas: permits needed for larger groups, amplified sound, tables or structures. Check NYC Parks and NYPD rules.</t>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
-      <text>
-        <t>e.g. 'same week', '4+ weeks'.</t>
+        <t>Date someone last confirmed these details (YYYY-MM-DD).</t>
       </text>
     </comment>
     <comment ref="Z1" authorId="0" shapeId="0">
-      <text>
-        <t>When events work here: weeknights, weekend afternoons, etc.</t>
-      </text>
-    </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
-      <text>
-        <t>Can a wheelchair user get in without stairs?</t>
-      </text>
-    </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
-      <text>
-        <t>Elevator, ramp, lighting, seating with backs, quiet corner.</t>
-      </text>
-    </comment>
-    <comment ref="AH1" authorId="0" shapeId="0">
-      <text>
-        <t>For a record player, projector or soldering irons.</t>
-      </text>
-    </comment>
-    <comment ref="AJ1" authorId="0" shapeId="0">
-      <text>
-        <t>For screenings.</t>
-      </text>
-    </comment>
-    <comment ref="AK1" authorId="0" shapeId="0">
-      <text>
-        <t>Subway lines and stop.</t>
-      </text>
-    </comment>
-    <comment ref="AN1" authorId="0" shapeId="0">
-      <text>
-        <t>A venue's own public form or events email page.</t>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0">
-      <text>
-        <t>Who to talk to about events (role is fine if no name).</t>
-      </text>
-    </comment>
-    <comment ref="AP1" authorId="0" shapeId="0">
-      <text>
-        <t>e.g. owner, events manager, librarian.</t>
-      </text>
-    </comment>
-    <comment ref="AQ1" authorId="0" shapeId="0">
-      <text>
-        <t>Prefer a business or events address over a personal one.</t>
-      </text>
-    </comment>
-    <comment ref="AR1" authorId="0" shapeId="0">
-      <text>
-        <t>Business line only.</t>
-      </text>
-    </comment>
-    <comment ref="AS1" authorId="0" shapeId="0">
-      <text>
-        <t>Only Yes if the venue has agreed. Otherwise the site shows the public booking link only.</t>
-      </text>
-    </comment>
-    <comment ref="AT1" authorId="0" shapeId="0">
-      <text>
-        <t>Who in the community knows them, past events, any history to be aware of.</t>
-      </text>
-    </comment>
-    <comment ref="AU1" authorId="0" shapeId="0">
-      <text>
-        <t>Practical tips: where to set up, what's worked, what to avoid.</t>
-      </text>
-    </comment>
-    <comment ref="AV1" authorId="0" shapeId="0">
-      <text>
-        <t>Date someone last confirmed these details (YYYY-MM-DD).</t>
-      </text>
-    </comment>
-    <comment ref="AX1" authorId="0" shapeId="0">
       <text>
         <t>Who added the venue.</t>
       </text>
@@ -757,58 +708,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>How to contribute</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Add details to a venue: fill in any blank cell on the Venues tab. Estimates are fine; note them in 'Notes for hosts'. Update 'Last verified' when you confirm something.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Add details to a venue: fill in any blank cell on the Venues tab. Estimates are fine. Update 'Last verified' when you confirm something.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Venue notes are freeform: How to book, Contact, Food &amp; drink, Accessibility, A/V equipment and Other notes. Write them the way you'd tell a friend who's hosting there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Add a new venue: add a row at the bottom, set Status to 'Pending review', fill in at least name, venue type, street address and borough, and put your name in 'Submitted by'. A maintainer approves it.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Public venues only. Never add a private home, or an address an organizer shares only by email or RSVP.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Contact details stay with collaborators. The site never shows contact name, email, phone or relationship notes unless 'OK to show contact publicly?' is Yes, which needs the venue's agreement.</t>
-        </is>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Everything in the Venue notes columns is shown on the public site, Contact included. Personal names, emails, phones and relationship notes go only in the 'Collaborators only' columns, which never leave the sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Don't change Venue ID once it's set. It's the venue's web address on Unplugg.Me.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Don't edit the 'Off Tech history' or 'Past events' tabs. They're rebuilt from the newsletter archive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Column headers have notes explaining each field. The full list is on the Field guide tab.</t>
         </is>
       </c>
     </row>
@@ -823,5342 +774,3141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX53"/>
+  <dimension ref="A1:Z53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="29" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="27" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="44" customWidth="1" min="16" max="16"/>
+    <col width="44" customWidth="1" min="17" max="17"/>
+    <col width="44" customWidth="1" min="18" max="18"/>
+    <col width="44" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
     <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="20" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
-    <col width="23" customWidth="1" min="33" max="33"/>
-    <col width="17" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
-    <col width="22" customWidth="1" min="36" max="36"/>
-    <col width="19" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="33" customWidth="1" min="40" max="40"/>
-    <col width="15" customWidth="1" min="41" max="41"/>
-    <col width="16" customWidth="1" min="42" max="42"/>
-    <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="17" customWidth="1" min="44" max="44"/>
-    <col width="32" customWidth="1" min="45" max="45"/>
-    <col width="22" customWidth="1" min="46" max="46"/>
-    <col width="19" customWidth="1" min="47" max="47"/>
-    <col width="17" customWidth="1" min="48" max="48"/>
-    <col width="15" customWidth="1" min="49" max="49"/>
-    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Venue ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Venue name</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Venue type</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Street address</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Neighborhood</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Borough</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="23" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="23" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="23" t="inlineStr">
         <is>
           <t>Location precision</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="23" t="inlineStr">
         <is>
           <t>Indoor / outdoor</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
-        <is>
-          <t>Capacity, standing (est.)</t>
-        </is>
-      </c>
-      <c r="M1" s="5" t="inlineStr">
-        <is>
-          <t>Capacity, seated (est.)</t>
-        </is>
-      </c>
-      <c r="N1" s="5" t="inlineStr">
-        <is>
-          <t>Seating</t>
-        </is>
-      </c>
-      <c r="O1" s="5" t="inlineStr">
-        <is>
-          <t>Tables available</t>
-        </is>
-      </c>
-      <c r="P1" s="5" t="inlineStr">
-        <is>
-          <t>Private room / buyout</t>
-        </is>
-      </c>
-      <c r="Q1" s="5" t="inlineStr">
-        <is>
-          <t>Weather backup</t>
-        </is>
-      </c>
-      <c r="R1" s="6" t="inlineStr">
-        <is>
-          <t>Noise level</t>
-        </is>
-      </c>
-      <c r="S1" s="6" t="inlineStr">
-        <is>
-          <t>Amplified sound allowed</t>
-        </is>
-      </c>
-      <c r="T1" s="6" t="inlineStr">
-        <is>
-          <t>Phone-free friendly</t>
-        </is>
-      </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="L1" s="23" t="inlineStr">
+        <is>
+          <t>Capacity (est.)</t>
+        </is>
+      </c>
+      <c r="M1" s="23" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>Cost notes</t>
-        </is>
-      </c>
-      <c r="W1" s="7" t="inlineStr">
+      <c r="N1" s="23" t="inlineStr">
         <is>
           <t>How to book</t>
         </is>
       </c>
-      <c r="X1" s="7" t="inlineStr">
-        <is>
-          <t>Permit notes</t>
-        </is>
-      </c>
-      <c r="Y1" s="7" t="inlineStr">
-        <is>
-          <t>Booking lead time</t>
-        </is>
-      </c>
-      <c r="Z1" s="7" t="inlineStr">
-        <is>
-          <t>Hours / best times</t>
-        </is>
-      </c>
-      <c r="AA1" s="8" t="inlineStr">
+      <c r="O1" s="23" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="P1" s="23" t="inlineStr">
         <is>
           <t>Food &amp; drink</t>
         </is>
       </c>
-      <c r="AB1" s="8" t="inlineStr">
-        <is>
-          <t>Alcohol</t>
-        </is>
-      </c>
-      <c r="AC1" s="8" t="inlineStr">
-        <is>
-          <t>All ages</t>
-        </is>
-      </c>
-      <c r="AD1" s="8" t="inlineStr">
-        <is>
-          <t>Restrooms</t>
-        </is>
-      </c>
-      <c r="AE1" s="9" t="inlineStr">
-        <is>
-          <t>Step-free access</t>
-        </is>
-      </c>
-      <c r="AF1" s="9" t="inlineStr">
-        <is>
-          <t>Accessible restroom</t>
-        </is>
-      </c>
-      <c r="AG1" s="9" t="inlineStr">
-        <is>
-          <t>Accessibility notes</t>
-        </is>
-      </c>
-      <c r="AH1" s="10" t="inlineStr">
-        <is>
-          <t>Power outlets</t>
-        </is>
-      </c>
-      <c r="AI1" s="10" t="inlineStr">
-        <is>
-          <t>Sound system / mic</t>
-        </is>
-      </c>
-      <c r="AJ1" s="10" t="inlineStr">
-        <is>
-          <t>Projector / screen</t>
-        </is>
-      </c>
-      <c r="AK1" s="4" t="inlineStr">
-        <is>
-          <t>Nearest transit</t>
-        </is>
-      </c>
-      <c r="AL1" s="11" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="AM1" s="11" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="AN1" s="11" t="inlineStr">
-        <is>
-          <t>Public booking / inquiry link</t>
-        </is>
-      </c>
-      <c r="AO1" s="12" t="inlineStr">
+      <c r="Q1" s="23" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="R1" s="23" t="inlineStr">
+        <is>
+          <t>A/V equipment</t>
+        </is>
+      </c>
+      <c r="S1" s="23" t="inlineStr">
+        <is>
+          <t>Other notes</t>
+        </is>
+      </c>
+      <c r="T1" s="23" t="inlineStr">
         <is>
           <t>Key contact</t>
         </is>
       </c>
-      <c r="AP1" s="12" t="inlineStr">
-        <is>
-          <t>Contact role</t>
-        </is>
-      </c>
-      <c r="AQ1" s="12" t="inlineStr">
+      <c r="U1" s="23" t="inlineStr">
         <is>
           <t>Contact email</t>
         </is>
       </c>
-      <c r="AR1" s="12" t="inlineStr">
+      <c r="V1" s="23" t="inlineStr">
         <is>
           <t>Contact phone</t>
         </is>
       </c>
-      <c r="AS1" s="12" t="inlineStr">
-        <is>
-          <t>OK to show contact publicly?</t>
-        </is>
-      </c>
-      <c r="AT1" s="12" t="inlineStr">
+      <c r="W1" s="23" t="inlineStr">
         <is>
           <t>Relationship notes</t>
         </is>
       </c>
-      <c r="AU1" s="13" t="inlineStr">
-        <is>
-          <t>Notes for hosts</t>
-        </is>
-      </c>
-      <c r="AV1" s="14" t="inlineStr">
+      <c r="X1" s="23" t="inlineStr">
         <is>
           <t>Last verified</t>
         </is>
       </c>
-      <c r="AW1" s="14" t="inlineStr">
+      <c r="Y1" s="23" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="AX1" s="14" t="inlineStr">
+      <c r="Z1" s="23" t="inlineStr">
         <is>
           <t>Submitted by</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>tompkins-square-park</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Tompkins Square Park</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Ave A to Ave B, E 7th to E 10th St, Manhattan</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H2" s="15" t="n">
+      <c r="H2" t="n">
         <v>40.7265</v>
       </c>
-      <c r="I2" s="15" t="n">
+      <c r="I2" t="n">
         <v>-73.9817</v>
       </c>
-      <c r="J2" s="15" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr"/>
-      <c r="M2" s="15" t="inlineStr"/>
-      <c r="N2" s="15" t="inlineStr"/>
-      <c r="O2" s="15" t="inlineStr"/>
-      <c r="P2" s="15" t="inlineStr"/>
-      <c r="Q2" s="15" t="inlineStr"/>
-      <c r="R2" s="15" t="inlineStr"/>
-      <c r="S2" s="15" t="inlineStr"/>
-      <c r="T2" s="15" t="inlineStr"/>
-      <c r="U2" s="15" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V2" s="15" t="inlineStr"/>
-      <c r="W2" s="15" t="inlineStr"/>
-      <c r="X2" s="15" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y2" s="15" t="inlineStr"/>
-      <c r="Z2" s="15" t="inlineStr"/>
-      <c r="AA2" s="15" t="inlineStr"/>
-      <c r="AB2" s="15" t="inlineStr"/>
-      <c r="AC2" s="15" t="inlineStr"/>
-      <c r="AD2" s="15" t="inlineStr"/>
-      <c r="AE2" s="15" t="inlineStr"/>
-      <c r="AF2" s="15" t="inlineStr"/>
-      <c r="AG2" s="15" t="inlineStr"/>
-      <c r="AH2" s="15" t="inlineStr"/>
-      <c r="AI2" s="15" t="inlineStr"/>
-      <c r="AJ2" s="15" t="inlineStr"/>
-      <c r="AK2" s="15" t="inlineStr"/>
-      <c r="AL2" s="15" t="inlineStr"/>
-      <c r="AM2" s="15" t="inlineStr"/>
-      <c r="AN2" s="15" t="inlineStr"/>
-      <c r="AO2" s="15" t="inlineStr"/>
-      <c r="AP2" s="15" t="inlineStr"/>
-      <c r="AQ2" s="15" t="inlineStr"/>
-      <c r="AR2" s="15" t="inlineStr"/>
-      <c r="AS2" s="15" t="inlineStr"/>
-      <c r="AT2" s="15" t="inlineStr"/>
-      <c r="AU2" s="15" t="inlineStr"/>
-      <c r="AV2" s="15" t="inlineStr"/>
-      <c r="AW2" s="15" t="inlineStr"/>
-      <c r="AX2" s="15" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>strother-school-of-radical-attention</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Strother School of Radical Attention</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>55 Washington St, Ste 736, Brooklyn, NY 11201</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>DUMBO</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H3" s="15" t="n">
+      <c r="H3" t="n">
         <v>40.7024</v>
       </c>
-      <c r="I3" s="15" t="n">
+      <c r="I3" t="n">
         <v>-73.9897</v>
       </c>
-      <c r="J3" s="15" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K3" s="15" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L3" s="15" t="inlineStr"/>
-      <c r="M3" s="15" t="inlineStr"/>
-      <c r="N3" s="15" t="inlineStr"/>
-      <c r="O3" s="15" t="inlineStr"/>
-      <c r="P3" s="15" t="inlineStr"/>
-      <c r="Q3" s="15" t="inlineStr"/>
-      <c r="R3" s="15" t="inlineStr"/>
-      <c r="S3" s="15" t="inlineStr"/>
-      <c r="T3" s="15" t="inlineStr"/>
-      <c r="U3" s="15" t="inlineStr"/>
-      <c r="V3" s="15" t="inlineStr"/>
-      <c r="W3" s="15" t="inlineStr"/>
-      <c r="X3" s="15" t="inlineStr"/>
-      <c r="Y3" s="15" t="inlineStr"/>
-      <c r="Z3" s="15" t="inlineStr"/>
-      <c r="AA3" s="15" t="inlineStr"/>
-      <c r="AB3" s="15" t="inlineStr"/>
-      <c r="AC3" s="15" t="inlineStr"/>
-      <c r="AD3" s="15" t="inlineStr"/>
-      <c r="AE3" s="15" t="inlineStr"/>
-      <c r="AF3" s="15" t="inlineStr"/>
-      <c r="AG3" s="15" t="inlineStr"/>
-      <c r="AH3" s="15" t="inlineStr"/>
-      <c r="AI3" s="15" t="inlineStr"/>
-      <c r="AJ3" s="15" t="inlineStr"/>
-      <c r="AK3" s="15" t="inlineStr"/>
-      <c r="AL3" s="15" t="inlineStr"/>
-      <c r="AM3" s="15" t="inlineStr"/>
-      <c r="AN3" s="15" t="inlineStr"/>
-      <c r="AO3" s="15" t="inlineStr"/>
-      <c r="AP3" s="15" t="inlineStr"/>
-      <c r="AQ3" s="15" t="inlineStr"/>
-      <c r="AR3" s="15" t="inlineStr"/>
-      <c r="AS3" s="15" t="inlineStr"/>
-      <c r="AT3" s="15" t="inlineStr"/>
-      <c r="AU3" s="15" t="inlineStr"/>
-      <c r="AV3" s="15" t="inlineStr"/>
-      <c r="AW3" s="15" t="inlineStr"/>
-      <c r="AX3" s="15" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>stavros-niarchos-foundation-library</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Stavros Niarchos Foundation Library</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>455 Fifth Ave, New York, NY 10016</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Midtown</t>
         </is>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H4" s="15" t="n">
+      <c r="H4" t="n">
         <v>40.752</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" t="n">
         <v>-73.98139999999999</v>
       </c>
-      <c r="J4" s="15" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L4" s="15" t="inlineStr"/>
-      <c r="M4" s="15" t="inlineStr"/>
-      <c r="N4" s="15" t="inlineStr"/>
-      <c r="O4" s="15" t="inlineStr"/>
-      <c r="P4" s="15" t="inlineStr"/>
-      <c r="Q4" s="15" t="inlineStr"/>
-      <c r="R4" s="15" t="inlineStr"/>
-      <c r="S4" s="15" t="inlineStr"/>
-      <c r="T4" s="15" t="inlineStr"/>
-      <c r="U4" s="15" t="inlineStr"/>
-      <c r="V4" s="15" t="inlineStr"/>
-      <c r="W4" s="15" t="inlineStr"/>
-      <c r="X4" s="15" t="inlineStr"/>
-      <c r="Y4" s="15" t="inlineStr"/>
-      <c r="Z4" s="15" t="inlineStr"/>
-      <c r="AA4" s="15" t="inlineStr"/>
-      <c r="AB4" s="15" t="inlineStr"/>
-      <c r="AC4" s="15" t="inlineStr"/>
-      <c r="AD4" s="15" t="inlineStr"/>
-      <c r="AE4" s="15" t="inlineStr"/>
-      <c r="AF4" s="15" t="inlineStr"/>
-      <c r="AG4" s="15" t="inlineStr"/>
-      <c r="AH4" s="15" t="inlineStr"/>
-      <c r="AI4" s="15" t="inlineStr"/>
-      <c r="AJ4" s="15" t="inlineStr"/>
-      <c r="AK4" s="15" t="inlineStr"/>
-      <c r="AL4" s="15" t="inlineStr"/>
-      <c r="AM4" s="15" t="inlineStr"/>
-      <c r="AN4" s="15" t="inlineStr"/>
-      <c r="AO4" s="15" t="inlineStr"/>
-      <c r="AP4" s="15" t="inlineStr"/>
-      <c r="AQ4" s="15" t="inlineStr"/>
-      <c r="AR4" s="15" t="inlineStr"/>
-      <c r="AS4" s="15" t="inlineStr"/>
-      <c r="AT4" s="15" t="inlineStr"/>
-      <c r="AU4" s="15" t="inlineStr"/>
-      <c r="AV4" s="15" t="inlineStr"/>
-      <c r="AW4" s="15" t="inlineStr"/>
-      <c r="AX4" s="15" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>prospect-park</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Prospect Park</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr"/>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Prospect Park</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H5" s="15" t="n">
+      <c r="H5" t="n">
         <v>40.6602</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" t="n">
         <v>-73.96899999999999</v>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L5" s="15" t="inlineStr"/>
-      <c r="M5" s="15" t="inlineStr"/>
-      <c r="N5" s="15" t="inlineStr"/>
-      <c r="O5" s="15" t="inlineStr"/>
-      <c r="P5" s="15" t="inlineStr"/>
-      <c r="Q5" s="15" t="inlineStr"/>
-      <c r="R5" s="15" t="inlineStr"/>
-      <c r="S5" s="15" t="inlineStr"/>
-      <c r="T5" s="15" t="inlineStr"/>
-      <c r="U5" s="15" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V5" s="15" t="inlineStr"/>
-      <c r="W5" s="15" t="inlineStr"/>
-      <c r="X5" s="15" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y5" s="15" t="inlineStr"/>
-      <c r="Z5" s="15" t="inlineStr"/>
-      <c r="AA5" s="15" t="inlineStr"/>
-      <c r="AB5" s="15" t="inlineStr"/>
-      <c r="AC5" s="15" t="inlineStr"/>
-      <c r="AD5" s="15" t="inlineStr"/>
-      <c r="AE5" s="15" t="inlineStr"/>
-      <c r="AF5" s="15" t="inlineStr"/>
-      <c r="AG5" s="15" t="inlineStr"/>
-      <c r="AH5" s="15" t="inlineStr"/>
-      <c r="AI5" s="15" t="inlineStr"/>
-      <c r="AJ5" s="15" t="inlineStr"/>
-      <c r="AK5" s="15" t="inlineStr"/>
-      <c r="AL5" s="15" t="inlineStr"/>
-      <c r="AM5" s="15" t="inlineStr"/>
-      <c r="AN5" s="15" t="inlineStr"/>
-      <c r="AO5" s="15" t="inlineStr"/>
-      <c r="AP5" s="15" t="inlineStr"/>
-      <c r="AQ5" s="15" t="inlineStr"/>
-      <c r="AR5" s="15" t="inlineStr"/>
-      <c r="AS5" s="15" t="inlineStr"/>
-      <c r="AT5" s="15" t="inlineStr"/>
-      <c r="AU5" s="15" t="inlineStr"/>
-      <c r="AV5" s="15" t="inlineStr"/>
-      <c r="AW5" s="15" t="inlineStr"/>
-      <c r="AX5" s="15" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>15th-street-quaker-meeting-house</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>15th Street Quaker Meeting House</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Church / meeting house</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>15 Rutherford Pl, New York, NY 10003</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Stuyvesant Square</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" t="n">
         <v>40.7343</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" t="n">
         <v>-73.98439999999999</v>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L6" s="15" t="inlineStr"/>
-      <c r="M6" s="15" t="inlineStr"/>
-      <c r="N6" s="15" t="inlineStr"/>
-      <c r="O6" s="15" t="inlineStr"/>
-      <c r="P6" s="15" t="inlineStr"/>
-      <c r="Q6" s="15" t="inlineStr"/>
-      <c r="R6" s="15" t="inlineStr"/>
-      <c r="S6" s="15" t="inlineStr"/>
-      <c r="T6" s="15" t="inlineStr"/>
-      <c r="U6" s="15" t="inlineStr"/>
-      <c r="V6" s="15" t="inlineStr"/>
-      <c r="W6" s="15" t="inlineStr"/>
-      <c r="X6" s="15" t="inlineStr"/>
-      <c r="Y6" s="15" t="inlineStr"/>
-      <c r="Z6" s="15" t="inlineStr"/>
-      <c r="AA6" s="15" t="inlineStr"/>
-      <c r="AB6" s="15" t="inlineStr"/>
-      <c r="AC6" s="15" t="inlineStr"/>
-      <c r="AD6" s="15" t="inlineStr"/>
-      <c r="AE6" s="15" t="inlineStr"/>
-      <c r="AF6" s="15" t="inlineStr"/>
-      <c r="AG6" s="15" t="inlineStr"/>
-      <c r="AH6" s="15" t="inlineStr"/>
-      <c r="AI6" s="15" t="inlineStr"/>
-      <c r="AJ6" s="15" t="inlineStr"/>
-      <c r="AK6" s="15" t="inlineStr"/>
-      <c r="AL6" s="15" t="inlineStr"/>
-      <c r="AM6" s="15" t="inlineStr"/>
-      <c r="AN6" s="15" t="inlineStr"/>
-      <c r="AO6" s="15" t="inlineStr"/>
-      <c r="AP6" s="15" t="inlineStr"/>
-      <c r="AQ6" s="15" t="inlineStr"/>
-      <c r="AR6" s="15" t="inlineStr"/>
-      <c r="AS6" s="15" t="inlineStr"/>
-      <c r="AT6" s="15" t="inlineStr"/>
-      <c r="AU6" s="15" t="inlineStr"/>
-      <c r="AV6" s="15" t="inlineStr"/>
-      <c r="AW6" s="15" t="inlineStr"/>
-      <c r="AX6" s="15" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>washington-square-park</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Washington Square Park</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr"/>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Greenwich Village</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" t="n">
         <v>40.7308</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" t="n">
         <v>-73.9973</v>
       </c>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K7" s="15" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L7" s="15" t="inlineStr"/>
-      <c r="M7" s="15" t="inlineStr"/>
-      <c r="N7" s="15" t="inlineStr"/>
-      <c r="O7" s="15" t="inlineStr"/>
-      <c r="P7" s="15" t="inlineStr"/>
-      <c r="Q7" s="15" t="inlineStr"/>
-      <c r="R7" s="15" t="inlineStr"/>
-      <c r="S7" s="15" t="inlineStr"/>
-      <c r="T7" s="15" t="inlineStr"/>
-      <c r="U7" s="15" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V7" s="15" t="inlineStr"/>
-      <c r="W7" s="15" t="inlineStr"/>
-      <c r="X7" s="15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y7" s="15" t="inlineStr"/>
-      <c r="Z7" s="15" t="inlineStr"/>
-      <c r="AA7" s="15" t="inlineStr"/>
-      <c r="AB7" s="15" t="inlineStr"/>
-      <c r="AC7" s="15" t="inlineStr"/>
-      <c r="AD7" s="15" t="inlineStr"/>
-      <c r="AE7" s="15" t="inlineStr"/>
-      <c r="AF7" s="15" t="inlineStr"/>
-      <c r="AG7" s="15" t="inlineStr"/>
-      <c r="AH7" s="15" t="inlineStr"/>
-      <c r="AI7" s="15" t="inlineStr"/>
-      <c r="AJ7" s="15" t="inlineStr"/>
-      <c r="AK7" s="15" t="inlineStr"/>
-      <c r="AL7" s="15" t="inlineStr"/>
-      <c r="AM7" s="15" t="inlineStr"/>
-      <c r="AN7" s="15" t="inlineStr"/>
-      <c r="AO7" s="15" t="inlineStr"/>
-      <c r="AP7" s="15" t="inlineStr"/>
-      <c r="AQ7" s="15" t="inlineStr"/>
-      <c r="AR7" s="15" t="inlineStr"/>
-      <c r="AS7" s="15" t="inlineStr"/>
-      <c r="AT7" s="15" t="inlineStr"/>
-      <c r="AU7" s="15" t="inlineStr"/>
-      <c r="AV7" s="15" t="inlineStr"/>
-      <c r="AW7" s="15" t="inlineStr"/>
-      <c r="AX7" s="15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>telos-haus</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>telos.haus</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>303 Ten Eyck St, 2nd Fl, Brooklyn, NY</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>East Williamsburg</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H8" s="15" t="n">
+      <c r="H8" t="n">
         <v>40.7087</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" t="n">
         <v>-73.93810000000001</v>
       </c>
-      <c r="J8" s="15" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K8" s="15" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L8" s="15" t="inlineStr"/>
-      <c r="M8" s="15" t="inlineStr"/>
-      <c r="N8" s="15" t="inlineStr"/>
-      <c r="O8" s="15" t="inlineStr"/>
-      <c r="P8" s="15" t="inlineStr"/>
-      <c r="Q8" s="15" t="inlineStr"/>
-      <c r="R8" s="15" t="inlineStr"/>
-      <c r="S8" s="15" t="inlineStr"/>
-      <c r="T8" s="15" t="inlineStr"/>
-      <c r="U8" s="15" t="inlineStr"/>
-      <c r="V8" s="15" t="inlineStr"/>
-      <c r="W8" s="15" t="inlineStr"/>
-      <c r="X8" s="15" t="inlineStr"/>
-      <c r="Y8" s="15" t="inlineStr"/>
-      <c r="Z8" s="15" t="inlineStr"/>
-      <c r="AA8" s="15" t="inlineStr"/>
-      <c r="AB8" s="15" t="inlineStr"/>
-      <c r="AC8" s="15" t="inlineStr"/>
-      <c r="AD8" s="15" t="inlineStr"/>
-      <c r="AE8" s="15" t="inlineStr"/>
-      <c r="AF8" s="15" t="inlineStr"/>
-      <c r="AG8" s="15" t="inlineStr"/>
-      <c r="AH8" s="15" t="inlineStr"/>
-      <c r="AI8" s="15" t="inlineStr"/>
-      <c r="AJ8" s="15" t="inlineStr"/>
-      <c r="AK8" s="15" t="inlineStr"/>
-      <c r="AL8" s="15" t="inlineStr"/>
-      <c r="AM8" s="15" t="inlineStr"/>
-      <c r="AN8" s="15" t="inlineStr"/>
-      <c r="AO8" s="15" t="inlineStr"/>
-      <c r="AP8" s="15" t="inlineStr"/>
-      <c r="AQ8" s="15" t="inlineStr"/>
-      <c r="AR8" s="15" t="inlineStr"/>
-      <c r="AS8" s="15" t="inlineStr"/>
-      <c r="AT8" s="15" t="inlineStr"/>
-      <c r="AU8" s="15" t="inlineStr"/>
-      <c r="AV8" s="15" t="inlineStr"/>
-      <c r="AW8" s="15" t="inlineStr"/>
-      <c r="AX8" s="15" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>fort-greene-park</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Fort Greene Park</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr"/>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Fort Greene</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H9" s="15" t="n">
+      <c r="H9" t="n">
         <v>40.6914</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" t="n">
         <v>-73.9757</v>
       </c>
-      <c r="J9" s="15" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K9" s="15" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L9" s="15" t="inlineStr"/>
-      <c r="M9" s="15" t="inlineStr"/>
-      <c r="N9" s="15" t="inlineStr"/>
-      <c r="O9" s="15" t="inlineStr"/>
-      <c r="P9" s="15" t="inlineStr"/>
-      <c r="Q9" s="15" t="inlineStr"/>
-      <c r="R9" s="15" t="inlineStr"/>
-      <c r="S9" s="15" t="inlineStr"/>
-      <c r="T9" s="15" t="inlineStr"/>
-      <c r="U9" s="15" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V9" s="15" t="inlineStr"/>
-      <c r="W9" s="15" t="inlineStr"/>
-      <c r="X9" s="15" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y9" s="15" t="inlineStr"/>
-      <c r="Z9" s="15" t="inlineStr"/>
-      <c r="AA9" s="15" t="inlineStr"/>
-      <c r="AB9" s="15" t="inlineStr"/>
-      <c r="AC9" s="15" t="inlineStr"/>
-      <c r="AD9" s="15" t="inlineStr"/>
-      <c r="AE9" s="15" t="inlineStr"/>
-      <c r="AF9" s="15" t="inlineStr"/>
-      <c r="AG9" s="15" t="inlineStr"/>
-      <c r="AH9" s="15" t="inlineStr"/>
-      <c r="AI9" s="15" t="inlineStr"/>
-      <c r="AJ9" s="15" t="inlineStr"/>
-      <c r="AK9" s="15" t="inlineStr"/>
-      <c r="AL9" s="15" t="inlineStr"/>
-      <c r="AM9" s="15" t="inlineStr"/>
-      <c r="AN9" s="15" t="inlineStr"/>
-      <c r="AO9" s="15" t="inlineStr"/>
-      <c r="AP9" s="15" t="inlineStr"/>
-      <c r="AQ9" s="15" t="inlineStr"/>
-      <c r="AR9" s="15" t="inlineStr"/>
-      <c r="AS9" s="15" t="inlineStr"/>
-      <c r="AT9" s="15" t="inlineStr"/>
-      <c r="AU9" s="15" t="inlineStr"/>
-      <c r="AV9" s="15" t="inlineStr"/>
-      <c r="AW9" s="15" t="inlineStr"/>
-      <c r="AX9" s="15" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>brooklyn-public-library-central-library</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Brooklyn Public Library – Central Library</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr"/>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Grand Army Plaza</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" t="n">
         <v>40.6724</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" t="n">
         <v>-73.9682</v>
       </c>
-      <c r="J10" s="15" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K10" s="15" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L10" s="15" t="inlineStr"/>
-      <c r="M10" s="15" t="inlineStr"/>
-      <c r="N10" s="15" t="inlineStr"/>
-      <c r="O10" s="15" t="inlineStr"/>
-      <c r="P10" s="15" t="inlineStr"/>
-      <c r="Q10" s="15" t="inlineStr"/>
-      <c r="R10" s="15" t="inlineStr"/>
-      <c r="S10" s="15" t="inlineStr"/>
-      <c r="T10" s="15" t="inlineStr"/>
-      <c r="U10" s="15" t="inlineStr"/>
-      <c r="V10" s="15" t="inlineStr"/>
-      <c r="W10" s="15" t="inlineStr"/>
-      <c r="X10" s="15" t="inlineStr"/>
-      <c r="Y10" s="15" t="inlineStr"/>
-      <c r="Z10" s="15" t="inlineStr"/>
-      <c r="AA10" s="15" t="inlineStr"/>
-      <c r="AB10" s="15" t="inlineStr"/>
-      <c r="AC10" s="15" t="inlineStr"/>
-      <c r="AD10" s="15" t="inlineStr"/>
-      <c r="AE10" s="15" t="inlineStr"/>
-      <c r="AF10" s="15" t="inlineStr"/>
-      <c r="AG10" s="15" t="inlineStr"/>
-      <c r="AH10" s="15" t="inlineStr"/>
-      <c r="AI10" s="15" t="inlineStr"/>
-      <c r="AJ10" s="15" t="inlineStr"/>
-      <c r="AK10" s="15" t="inlineStr"/>
-      <c r="AL10" s="15" t="inlineStr"/>
-      <c r="AM10" s="15" t="inlineStr"/>
-      <c r="AN10" s="15" t="inlineStr"/>
-      <c r="AO10" s="15" t="inlineStr"/>
-      <c r="AP10" s="15" t="inlineStr"/>
-      <c r="AQ10" s="15" t="inlineStr"/>
-      <c r="AR10" s="15" t="inlineStr"/>
-      <c r="AS10" s="15" t="inlineStr"/>
-      <c r="AT10" s="15" t="inlineStr"/>
-      <c r="AU10" s="15" t="inlineStr"/>
-      <c r="AV10" s="15" t="inlineStr"/>
-      <c r="AW10" s="15" t="inlineStr"/>
-      <c r="AX10" s="15" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>cornerstone-makerspace</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Cornerstone Makerspace</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Makerspace</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>178 Bennett Ave, New York, NY 10040</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Washington Heights</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" t="n">
         <v>40.8571</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" t="n">
         <v>-73.9318</v>
       </c>
-      <c r="J11" s="15" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K11" s="15" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L11" s="15" t="inlineStr"/>
-      <c r="M11" s="15" t="inlineStr"/>
-      <c r="N11" s="15" t="inlineStr"/>
-      <c r="O11" s="15" t="inlineStr"/>
-      <c r="P11" s="15" t="inlineStr"/>
-      <c r="Q11" s="15" t="inlineStr"/>
-      <c r="R11" s="15" t="inlineStr"/>
-      <c r="S11" s="15" t="inlineStr"/>
-      <c r="T11" s="15" t="inlineStr"/>
-      <c r="U11" s="15" t="inlineStr"/>
-      <c r="V11" s="15" t="inlineStr"/>
-      <c r="W11" s="15" t="inlineStr"/>
-      <c r="X11" s="15" t="inlineStr"/>
-      <c r="Y11" s="15" t="inlineStr"/>
-      <c r="Z11" s="15" t="inlineStr"/>
-      <c r="AA11" s="15" t="inlineStr"/>
-      <c r="AB11" s="15" t="inlineStr"/>
-      <c r="AC11" s="15" t="inlineStr"/>
-      <c r="AD11" s="15" t="inlineStr"/>
-      <c r="AE11" s="15" t="inlineStr"/>
-      <c r="AF11" s="15" t="inlineStr"/>
-      <c r="AG11" s="15" t="inlineStr"/>
-      <c r="AH11" s="15" t="inlineStr"/>
-      <c r="AI11" s="15" t="inlineStr"/>
-      <c r="AJ11" s="15" t="inlineStr"/>
-      <c r="AK11" s="15" t="inlineStr"/>
-      <c r="AL11" s="15" t="inlineStr"/>
-      <c r="AM11" s="15" t="inlineStr"/>
-      <c r="AN11" s="15" t="inlineStr"/>
-      <c r="AO11" s="15" t="inlineStr"/>
-      <c r="AP11" s="15" t="inlineStr"/>
-      <c r="AQ11" s="15" t="inlineStr"/>
-      <c r="AR11" s="15" t="inlineStr"/>
-      <c r="AS11" s="15" t="inlineStr"/>
-      <c r="AT11" s="15" t="inlineStr"/>
-      <c r="AU11" s="15" t="inlineStr"/>
-      <c r="AV11" s="15" t="inlineStr"/>
-      <c r="AW11" s="15" t="inlineStr"/>
-      <c r="AX11" s="15" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>875-third-ave</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>875 Third Ave. (POPS, Lower Level)</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Privately owned public space (POPS)</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>875 Third Ave, Lower Level, New York, NY 10022</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Midtown East</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H12" s="15" t="n">
+      <c r="H12" t="n">
         <v>40.7566</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" t="n">
         <v>-73.97</v>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L12" s="15" t="inlineStr"/>
-      <c r="M12" s="15" t="inlineStr"/>
-      <c r="N12" s="15" t="inlineStr"/>
-      <c r="O12" s="15" t="inlineStr"/>
-      <c r="P12" s="15" t="inlineStr"/>
-      <c r="Q12" s="15" t="inlineStr"/>
-      <c r="R12" s="15" t="inlineStr"/>
-      <c r="S12" s="15" t="inlineStr"/>
-      <c r="T12" s="15" t="inlineStr"/>
-      <c r="U12" s="15" t="inlineStr"/>
-      <c r="V12" s="15" t="inlineStr"/>
-      <c r="W12" s="15" t="inlineStr"/>
-      <c r="X12" s="15" t="inlineStr"/>
-      <c r="Y12" s="15" t="inlineStr"/>
-      <c r="Z12" s="15" t="inlineStr"/>
-      <c r="AA12" s="15" t="inlineStr"/>
-      <c r="AB12" s="15" t="inlineStr"/>
-      <c r="AC12" s="15" t="inlineStr"/>
-      <c r="AD12" s="15" t="inlineStr"/>
-      <c r="AE12" s="15" t="inlineStr"/>
-      <c r="AF12" s="15" t="inlineStr"/>
-      <c r="AG12" s="15" t="inlineStr"/>
-      <c r="AH12" s="15" t="inlineStr"/>
-      <c r="AI12" s="15" t="inlineStr"/>
-      <c r="AJ12" s="15" t="inlineStr"/>
-      <c r="AK12" s="15" t="inlineStr"/>
-      <c r="AL12" s="15" t="inlineStr"/>
-      <c r="AM12" s="15" t="inlineStr"/>
-      <c r="AN12" s="15" t="inlineStr"/>
-      <c r="AO12" s="15" t="inlineStr"/>
-      <c r="AP12" s="15" t="inlineStr"/>
-      <c r="AQ12" s="15" t="inlineStr"/>
-      <c r="AR12" s="15" t="inlineStr"/>
-      <c r="AS12" s="15" t="inlineStr"/>
-      <c r="AT12" s="15" t="inlineStr"/>
-      <c r="AU12" s="15" t="inlineStr"/>
-      <c r="AV12" s="15" t="inlineStr"/>
-      <c r="AW12" s="15" t="inlineStr"/>
-      <c r="AX12" s="15" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>columbia-university</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Columbia University</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr"/>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Morningside Heights</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" t="n">
         <v>40.8075</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" t="n">
         <v>-73.96259999999999</v>
       </c>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L13" s="15" t="inlineStr"/>
-      <c r="M13" s="15" t="inlineStr"/>
-      <c r="N13" s="15" t="inlineStr"/>
-      <c r="O13" s="15" t="inlineStr"/>
-      <c r="P13" s="15" t="inlineStr"/>
-      <c r="Q13" s="15" t="inlineStr"/>
-      <c r="R13" s="15" t="inlineStr"/>
-      <c r="S13" s="15" t="inlineStr"/>
-      <c r="T13" s="15" t="inlineStr"/>
-      <c r="U13" s="15" t="inlineStr"/>
-      <c r="V13" s="15" t="inlineStr"/>
-      <c r="W13" s="15" t="inlineStr"/>
-      <c r="X13" s="15" t="inlineStr"/>
-      <c r="Y13" s="15" t="inlineStr"/>
-      <c r="Z13" s="15" t="inlineStr"/>
-      <c r="AA13" s="15" t="inlineStr"/>
-      <c r="AB13" s="15" t="inlineStr"/>
-      <c r="AC13" s="15" t="inlineStr"/>
-      <c r="AD13" s="15" t="inlineStr"/>
-      <c r="AE13" s="15" t="inlineStr"/>
-      <c r="AF13" s="15" t="inlineStr"/>
-      <c r="AG13" s="15" t="inlineStr"/>
-      <c r="AH13" s="15" t="inlineStr"/>
-      <c r="AI13" s="15" t="inlineStr"/>
-      <c r="AJ13" s="15" t="inlineStr"/>
-      <c r="AK13" s="15" t="inlineStr"/>
-      <c r="AL13" s="15" t="inlineStr"/>
-      <c r="AM13" s="15" t="inlineStr"/>
-      <c r="AN13" s="15" t="inlineStr"/>
-      <c r="AO13" s="15" t="inlineStr"/>
-      <c r="AP13" s="15" t="inlineStr"/>
-      <c r="AQ13" s="15" t="inlineStr"/>
-      <c r="AR13" s="15" t="inlineStr"/>
-      <c r="AS13" s="15" t="inlineStr"/>
-      <c r="AT13" s="15" t="inlineStr"/>
-      <c r="AU13" s="15" t="inlineStr"/>
-      <c r="AV13" s="15" t="inlineStr"/>
-      <c r="AW13" s="15" t="inlineStr"/>
-      <c r="AX13" s="15" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>jefferson-market-library</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Jefferson Market Library</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr"/>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Greenwich Village</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H14" t="n">
         <v>40.7344</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I14" t="n">
         <v>-73.999</v>
       </c>
-      <c r="J14" s="15" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr"/>
-      <c r="M14" s="15" t="inlineStr"/>
-      <c r="N14" s="15" t="inlineStr"/>
-      <c r="O14" s="15" t="inlineStr"/>
-      <c r="P14" s="15" t="inlineStr"/>
-      <c r="Q14" s="15" t="inlineStr"/>
-      <c r="R14" s="15" t="inlineStr"/>
-      <c r="S14" s="15" t="inlineStr"/>
-      <c r="T14" s="15" t="inlineStr"/>
-      <c r="U14" s="15" t="inlineStr"/>
-      <c r="V14" s="15" t="inlineStr"/>
-      <c r="W14" s="15" t="inlineStr"/>
-      <c r="X14" s="15" t="inlineStr"/>
-      <c r="Y14" s="15" t="inlineStr"/>
-      <c r="Z14" s="15" t="inlineStr"/>
-      <c r="AA14" s="15" t="inlineStr"/>
-      <c r="AB14" s="15" t="inlineStr"/>
-      <c r="AC14" s="15" t="inlineStr"/>
-      <c r="AD14" s="15" t="inlineStr"/>
-      <c r="AE14" s="15" t="inlineStr"/>
-      <c r="AF14" s="15" t="inlineStr"/>
-      <c r="AG14" s="15" t="inlineStr"/>
-      <c r="AH14" s="15" t="inlineStr"/>
-      <c r="AI14" s="15" t="inlineStr"/>
-      <c r="AJ14" s="15" t="inlineStr"/>
-      <c r="AK14" s="15" t="inlineStr"/>
-      <c r="AL14" s="15" t="inlineStr"/>
-      <c r="AM14" s="15" t="inlineStr"/>
-      <c r="AN14" s="15" t="inlineStr"/>
-      <c r="AO14" s="15" t="inlineStr"/>
-      <c r="AP14" s="15" t="inlineStr"/>
-      <c r="AQ14" s="15" t="inlineStr"/>
-      <c r="AR14" s="15" t="inlineStr"/>
-      <c r="AS14" s="15" t="inlineStr"/>
-      <c r="AT14" s="15" t="inlineStr"/>
-      <c r="AU14" s="15" t="inlineStr"/>
-      <c r="AV14" s="15" t="inlineStr"/>
-      <c r="AW14" s="15" t="inlineStr"/>
-      <c r="AX14" s="15" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>208-w-13th-st</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>208 W 13th St. (ITAA meeting)</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>208 W 13th St, New York, NY 10011</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>West Village</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H15" t="n">
         <v>40.7381</v>
       </c>
-      <c r="I15" s="15" t="n">
+      <c r="I15" t="n">
         <v>-74.001</v>
       </c>
-      <c r="J15" s="15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr"/>
-      <c r="M15" s="15" t="inlineStr"/>
-      <c r="N15" s="15" t="inlineStr"/>
-      <c r="O15" s="15" t="inlineStr"/>
-      <c r="P15" s="15" t="inlineStr"/>
-      <c r="Q15" s="15" t="inlineStr"/>
-      <c r="R15" s="15" t="inlineStr"/>
-      <c r="S15" s="15" t="inlineStr"/>
-      <c r="T15" s="15" t="inlineStr"/>
-      <c r="U15" s="15" t="inlineStr"/>
-      <c r="V15" s="15" t="inlineStr"/>
-      <c r="W15" s="15" t="inlineStr"/>
-      <c r="X15" s="15" t="inlineStr"/>
-      <c r="Y15" s="15" t="inlineStr"/>
-      <c r="Z15" s="15" t="inlineStr"/>
-      <c r="AA15" s="15" t="inlineStr"/>
-      <c r="AB15" s="15" t="inlineStr"/>
-      <c r="AC15" s="15" t="inlineStr"/>
-      <c r="AD15" s="15" t="inlineStr"/>
-      <c r="AE15" s="15" t="inlineStr"/>
-      <c r="AF15" s="15" t="inlineStr"/>
-      <c r="AG15" s="15" t="inlineStr"/>
-      <c r="AH15" s="15" t="inlineStr"/>
-      <c r="AI15" s="15" t="inlineStr"/>
-      <c r="AJ15" s="15" t="inlineStr"/>
-      <c r="AK15" s="15" t="inlineStr"/>
-      <c r="AL15" s="15" t="inlineStr"/>
-      <c r="AM15" s="15" t="inlineStr"/>
-      <c r="AN15" s="15" t="inlineStr"/>
-      <c r="AO15" s="15" t="inlineStr"/>
-      <c r="AP15" s="15" t="inlineStr"/>
-      <c r="AQ15" s="15" t="inlineStr"/>
-      <c r="AR15" s="15" t="inlineStr"/>
-      <c r="AS15" s="15" t="inlineStr"/>
-      <c r="AT15" s="15" t="inlineStr"/>
-      <c r="AU15" s="15" t="inlineStr"/>
-      <c r="AV15" s="15" t="inlineStr"/>
-      <c r="AW15" s="15" t="inlineStr"/>
-      <c r="AX15" s="15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>t-j-byrnes</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>T.J. Byrnes</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Bar / cafe / restaurant</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>77 Fulton St, New York, NY 10038</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Financial District</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H16" t="n">
         <v>40.7085</v>
       </c>
-      <c r="I16" s="15" t="n">
+      <c r="I16" t="n">
         <v>-74.004</v>
       </c>
-      <c r="J16" s="15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K16" s="15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L16" s="15" t="inlineStr"/>
-      <c r="M16" s="15" t="inlineStr"/>
-      <c r="N16" s="15" t="inlineStr"/>
-      <c r="O16" s="15" t="inlineStr"/>
-      <c r="P16" s="15" t="inlineStr"/>
-      <c r="Q16" s="15" t="inlineStr"/>
-      <c r="R16" s="15" t="inlineStr"/>
-      <c r="S16" s="15" t="inlineStr"/>
-      <c r="T16" s="15" t="inlineStr"/>
-      <c r="U16" s="15" t="inlineStr"/>
-      <c r="V16" s="15" t="inlineStr"/>
-      <c r="W16" s="15" t="inlineStr"/>
-      <c r="X16" s="15" t="inlineStr"/>
-      <c r="Y16" s="15" t="inlineStr"/>
-      <c r="Z16" s="15" t="inlineStr"/>
-      <c r="AA16" s="15" t="inlineStr"/>
-      <c r="AB16" s="15" t="inlineStr"/>
-      <c r="AC16" s="15" t="inlineStr"/>
-      <c r="AD16" s="15" t="inlineStr"/>
-      <c r="AE16" s="15" t="inlineStr"/>
-      <c r="AF16" s="15" t="inlineStr"/>
-      <c r="AG16" s="15" t="inlineStr"/>
-      <c r="AH16" s="15" t="inlineStr"/>
-      <c r="AI16" s="15" t="inlineStr"/>
-      <c r="AJ16" s="15" t="inlineStr"/>
-      <c r="AK16" s="15" t="inlineStr"/>
-      <c r="AL16" s="15" t="inlineStr"/>
-      <c r="AM16" s="15" t="inlineStr"/>
-      <c r="AN16" s="15" t="inlineStr"/>
-      <c r="AO16" s="15" t="inlineStr"/>
-      <c r="AP16" s="15" t="inlineStr"/>
-      <c r="AQ16" s="15" t="inlineStr"/>
-      <c r="AR16" s="15" t="inlineStr"/>
-      <c r="AS16" s="15" t="inlineStr"/>
-      <c r="AT16" s="15" t="inlineStr"/>
-      <c r="AU16" s="15" t="inlineStr"/>
-      <c r="AV16" s="15" t="inlineStr"/>
-      <c r="AW16" s="15" t="inlineStr"/>
-      <c r="AX16" s="15" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>222-bowery</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>222 Bowery (Giorno Poetry Systems)</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>222 Bowery, New York, NY 10012</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Bowery</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" t="n">
         <v>40.7224</v>
       </c>
-      <c r="I17" s="15" t="n">
+      <c r="I17" t="n">
         <v>-73.9933</v>
       </c>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K17" s="15" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L17" s="15" t="inlineStr"/>
-      <c r="M17" s="15" t="inlineStr"/>
-      <c r="N17" s="15" t="inlineStr"/>
-      <c r="O17" s="15" t="inlineStr"/>
-      <c r="P17" s="15" t="inlineStr"/>
-      <c r="Q17" s="15" t="inlineStr"/>
-      <c r="R17" s="15" t="inlineStr"/>
-      <c r="S17" s="15" t="inlineStr"/>
-      <c r="T17" s="15" t="inlineStr"/>
-      <c r="U17" s="15" t="inlineStr"/>
-      <c r="V17" s="15" t="inlineStr"/>
-      <c r="W17" s="15" t="inlineStr"/>
-      <c r="X17" s="15" t="inlineStr"/>
-      <c r="Y17" s="15" t="inlineStr"/>
-      <c r="Z17" s="15" t="inlineStr"/>
-      <c r="AA17" s="15" t="inlineStr"/>
-      <c r="AB17" s="15" t="inlineStr"/>
-      <c r="AC17" s="15" t="inlineStr"/>
-      <c r="AD17" s="15" t="inlineStr"/>
-      <c r="AE17" s="15" t="inlineStr"/>
-      <c r="AF17" s="15" t="inlineStr"/>
-      <c r="AG17" s="15" t="inlineStr"/>
-      <c r="AH17" s="15" t="inlineStr"/>
-      <c r="AI17" s="15" t="inlineStr"/>
-      <c r="AJ17" s="15" t="inlineStr"/>
-      <c r="AK17" s="15" t="inlineStr"/>
-      <c r="AL17" s="15" t="inlineStr"/>
-      <c r="AM17" s="15" t="inlineStr"/>
-      <c r="AN17" s="15" t="inlineStr"/>
-      <c r="AO17" s="15" t="inlineStr"/>
-      <c r="AP17" s="15" t="inlineStr"/>
-      <c r="AQ17" s="15" t="inlineStr"/>
-      <c r="AR17" s="15" t="inlineStr"/>
-      <c r="AS17" s="15" t="inlineStr"/>
-      <c r="AT17" s="15" t="inlineStr"/>
-      <c r="AU17" s="15" t="inlineStr"/>
-      <c r="AV17" s="15" t="inlineStr"/>
-      <c r="AW17" s="15" t="inlineStr"/>
-      <c r="AX17" s="15" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>boshis-place</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>boshi's place</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr"/>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>East Williamsburg</t>
         </is>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" t="n">
         <v>40.711</v>
       </c>
-      <c r="I18" s="15" t="n">
+      <c r="I18" t="n">
         <v>-73.93300000000001</v>
       </c>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>approx</t>
         </is>
       </c>
-      <c r="K18" s="15" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L18" s="15" t="inlineStr"/>
-      <c r="M18" s="15" t="inlineStr"/>
-      <c r="N18" s="15" t="inlineStr"/>
-      <c r="O18" s="15" t="inlineStr"/>
-      <c r="P18" s="15" t="inlineStr"/>
-      <c r="Q18" s="15" t="inlineStr"/>
-      <c r="R18" s="15" t="inlineStr"/>
-      <c r="S18" s="15" t="inlineStr"/>
-      <c r="T18" s="15" t="inlineStr"/>
-      <c r="U18" s="15" t="inlineStr"/>
-      <c r="V18" s="15" t="inlineStr"/>
-      <c r="W18" s="15" t="inlineStr"/>
-      <c r="X18" s="15" t="inlineStr"/>
-      <c r="Y18" s="15" t="inlineStr"/>
-      <c r="Z18" s="15" t="inlineStr"/>
-      <c r="AA18" s="15" t="inlineStr"/>
-      <c r="AB18" s="15" t="inlineStr"/>
-      <c r="AC18" s="15" t="inlineStr"/>
-      <c r="AD18" s="15" t="inlineStr"/>
-      <c r="AE18" s="15" t="inlineStr"/>
-      <c r="AF18" s="15" t="inlineStr"/>
-      <c r="AG18" s="15" t="inlineStr"/>
-      <c r="AH18" s="15" t="inlineStr"/>
-      <c r="AI18" s="15" t="inlineStr"/>
-      <c r="AJ18" s="15" t="inlineStr"/>
-      <c r="AK18" s="15" t="inlineStr"/>
-      <c r="AL18" s="15" t="inlineStr"/>
-      <c r="AM18" s="15" t="inlineStr"/>
-      <c r="AN18" s="15" t="inlineStr"/>
-      <c r="AO18" s="15" t="inlineStr"/>
-      <c r="AP18" s="15" t="inlineStr"/>
-      <c r="AQ18" s="15" t="inlineStr"/>
-      <c r="AR18" s="15" t="inlineStr"/>
-      <c r="AS18" s="15" t="inlineStr"/>
-      <c r="AT18" s="15" t="inlineStr"/>
-      <c r="AU18" s="15" t="inlineStr"/>
-      <c r="AV18" s="15" t="inlineStr"/>
-      <c r="AW18" s="15" t="inlineStr"/>
-      <c r="AX18" s="15" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>fort-tilden</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Fort Tilden</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr"/>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Rockaway</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Queens</t>
         </is>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" t="n">
         <v>40.5625</v>
       </c>
-      <c r="I19" s="15" t="n">
+      <c r="I19" t="n">
         <v>-73.8856</v>
       </c>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K19" s="15" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L19" s="15" t="inlineStr"/>
-      <c r="M19" s="15" t="inlineStr"/>
-      <c r="N19" s="15" t="inlineStr"/>
-      <c r="O19" s="15" t="inlineStr"/>
-      <c r="P19" s="15" t="inlineStr"/>
-      <c r="Q19" s="15" t="inlineStr"/>
-      <c r="R19" s="15" t="inlineStr"/>
-      <c r="S19" s="15" t="inlineStr"/>
-      <c r="T19" s="15" t="inlineStr"/>
-      <c r="U19" s="15" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V19" s="15" t="inlineStr"/>
-      <c r="W19" s="15" t="inlineStr"/>
-      <c r="X19" s="15" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y19" s="15" t="inlineStr"/>
-      <c r="Z19" s="15" t="inlineStr"/>
-      <c r="AA19" s="15" t="inlineStr"/>
-      <c r="AB19" s="15" t="inlineStr"/>
-      <c r="AC19" s="15" t="inlineStr"/>
-      <c r="AD19" s="15" t="inlineStr"/>
-      <c r="AE19" s="15" t="inlineStr"/>
-      <c r="AF19" s="15" t="inlineStr"/>
-      <c r="AG19" s="15" t="inlineStr"/>
-      <c r="AH19" s="15" t="inlineStr"/>
-      <c r="AI19" s="15" t="inlineStr"/>
-      <c r="AJ19" s="15" t="inlineStr"/>
-      <c r="AK19" s="15" t="inlineStr"/>
-      <c r="AL19" s="15" t="inlineStr"/>
-      <c r="AM19" s="15" t="inlineStr"/>
-      <c r="AN19" s="15" t="inlineStr"/>
-      <c r="AO19" s="15" t="inlineStr"/>
-      <c r="AP19" s="15" t="inlineStr"/>
-      <c r="AQ19" s="15" t="inlineStr"/>
-      <c r="AR19" s="15" t="inlineStr"/>
-      <c r="AS19" s="15" t="inlineStr"/>
-      <c r="AT19" s="15" t="inlineStr"/>
-      <c r="AU19" s="15" t="inlineStr"/>
-      <c r="AV19" s="15" t="inlineStr"/>
-      <c r="AW19" s="15" t="inlineStr"/>
-      <c r="AX19" s="15" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>lalins</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Lalin's</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Bar / cafe / restaurant</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>1131 Broadway, Brooklyn, NY 11221</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Bushwick</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" t="n">
         <v>40.6942</v>
       </c>
-      <c r="I20" s="15" t="n">
+      <c r="I20" t="n">
         <v>-73.9293</v>
       </c>
-      <c r="J20" s="15" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K20" s="15" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L20" s="15" t="inlineStr"/>
-      <c r="M20" s="15" t="inlineStr"/>
-      <c r="N20" s="15" t="inlineStr"/>
-      <c r="O20" s="15" t="inlineStr"/>
-      <c r="P20" s="15" t="inlineStr"/>
-      <c r="Q20" s="15" t="inlineStr"/>
-      <c r="R20" s="15" t="inlineStr"/>
-      <c r="S20" s="15" t="inlineStr"/>
-      <c r="T20" s="15" t="inlineStr"/>
-      <c r="U20" s="15" t="inlineStr"/>
-      <c r="V20" s="15" t="inlineStr"/>
-      <c r="W20" s="15" t="inlineStr"/>
-      <c r="X20" s="15" t="inlineStr"/>
-      <c r="Y20" s="15" t="inlineStr"/>
-      <c r="Z20" s="15" t="inlineStr"/>
-      <c r="AA20" s="15" t="inlineStr"/>
-      <c r="AB20" s="15" t="inlineStr"/>
-      <c r="AC20" s="15" t="inlineStr"/>
-      <c r="AD20" s="15" t="inlineStr"/>
-      <c r="AE20" s="15" t="inlineStr"/>
-      <c r="AF20" s="15" t="inlineStr"/>
-      <c r="AG20" s="15" t="inlineStr"/>
-      <c r="AH20" s="15" t="inlineStr"/>
-      <c r="AI20" s="15" t="inlineStr"/>
-      <c r="AJ20" s="15" t="inlineStr"/>
-      <c r="AK20" s="15" t="inlineStr"/>
-      <c r="AL20" s="15" t="inlineStr"/>
-      <c r="AM20" s="15" t="inlineStr"/>
-      <c r="AN20" s="15" t="inlineStr"/>
-      <c r="AO20" s="15" t="inlineStr"/>
-      <c r="AP20" s="15" t="inlineStr"/>
-      <c r="AQ20" s="15" t="inlineStr"/>
-      <c r="AR20" s="15" t="inlineStr"/>
-      <c r="AS20" s="15" t="inlineStr"/>
-      <c r="AT20" s="15" t="inlineStr"/>
-      <c r="AU20" s="15" t="inlineStr"/>
-      <c r="AV20" s="15" t="inlineStr"/>
-      <c r="AW20" s="15" t="inlineStr"/>
-      <c r="AX20" s="15" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>the-new-school</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>The New School</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr"/>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Greenwich Village</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H21" s="15" t="n">
+      <c r="H21" t="n">
         <v>40.7355</v>
       </c>
-      <c r="I21" s="15" t="n">
+      <c r="I21" t="n">
         <v>-73.9971</v>
       </c>
-      <c r="J21" s="15" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K21" s="15" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L21" s="15" t="inlineStr"/>
-      <c r="M21" s="15" t="inlineStr"/>
-      <c r="N21" s="15" t="inlineStr"/>
-      <c r="O21" s="15" t="inlineStr"/>
-      <c r="P21" s="15" t="inlineStr"/>
-      <c r="Q21" s="15" t="inlineStr"/>
-      <c r="R21" s="15" t="inlineStr"/>
-      <c r="S21" s="15" t="inlineStr"/>
-      <c r="T21" s="15" t="inlineStr"/>
-      <c r="U21" s="15" t="inlineStr"/>
-      <c r="V21" s="15" t="inlineStr"/>
-      <c r="W21" s="15" t="inlineStr"/>
-      <c r="X21" s="15" t="inlineStr"/>
-      <c r="Y21" s="15" t="inlineStr"/>
-      <c r="Z21" s="15" t="inlineStr"/>
-      <c r="AA21" s="15" t="inlineStr"/>
-      <c r="AB21" s="15" t="inlineStr"/>
-      <c r="AC21" s="15" t="inlineStr"/>
-      <c r="AD21" s="15" t="inlineStr"/>
-      <c r="AE21" s="15" t="inlineStr"/>
-      <c r="AF21" s="15" t="inlineStr"/>
-      <c r="AG21" s="15" t="inlineStr"/>
-      <c r="AH21" s="15" t="inlineStr"/>
-      <c r="AI21" s="15" t="inlineStr"/>
-      <c r="AJ21" s="15" t="inlineStr"/>
-      <c r="AK21" s="15" t="inlineStr"/>
-      <c r="AL21" s="15" t="inlineStr"/>
-      <c r="AM21" s="15" t="inlineStr"/>
-      <c r="AN21" s="15" t="inlineStr"/>
-      <c r="AO21" s="15" t="inlineStr"/>
-      <c r="AP21" s="15" t="inlineStr"/>
-      <c r="AQ21" s="15" t="inlineStr"/>
-      <c r="AR21" s="15" t="inlineStr"/>
-      <c r="AS21" s="15" t="inlineStr"/>
-      <c r="AT21" s="15" t="inlineStr"/>
-      <c r="AU21" s="15" t="inlineStr"/>
-      <c r="AV21" s="15" t="inlineStr"/>
-      <c r="AW21" s="15" t="inlineStr"/>
-      <c r="AX21" s="15" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>wonderville</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Wonderville</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Bar / cafe / restaurant</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr"/>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Bushwick</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H22" s="15" t="n">
+      <c r="H22" t="n">
         <v>40.6936</v>
       </c>
-      <c r="I22" s="15" t="n">
+      <c r="I22" t="n">
         <v>-73.9306</v>
       </c>
-      <c r="J22" s="15" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K22" s="15" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L22" s="15" t="inlineStr"/>
-      <c r="M22" s="15" t="inlineStr"/>
-      <c r="N22" s="15" t="inlineStr"/>
-      <c r="O22" s="15" t="inlineStr"/>
-      <c r="P22" s="15" t="inlineStr"/>
-      <c r="Q22" s="15" t="inlineStr"/>
-      <c r="R22" s="15" t="inlineStr"/>
-      <c r="S22" s="15" t="inlineStr"/>
-      <c r="T22" s="15" t="inlineStr"/>
-      <c r="U22" s="15" t="inlineStr"/>
-      <c r="V22" s="15" t="inlineStr"/>
-      <c r="W22" s="15" t="inlineStr"/>
-      <c r="X22" s="15" t="inlineStr"/>
-      <c r="Y22" s="15" t="inlineStr"/>
-      <c r="Z22" s="15" t="inlineStr"/>
-      <c r="AA22" s="15" t="inlineStr"/>
-      <c r="AB22" s="15" t="inlineStr"/>
-      <c r="AC22" s="15" t="inlineStr"/>
-      <c r="AD22" s="15" t="inlineStr"/>
-      <c r="AE22" s="15" t="inlineStr"/>
-      <c r="AF22" s="15" t="inlineStr"/>
-      <c r="AG22" s="15" t="inlineStr"/>
-      <c r="AH22" s="15" t="inlineStr"/>
-      <c r="AI22" s="15" t="inlineStr"/>
-      <c r="AJ22" s="15" t="inlineStr"/>
-      <c r="AK22" s="15" t="inlineStr"/>
-      <c r="AL22" s="15" t="inlineStr"/>
-      <c r="AM22" s="15" t="inlineStr"/>
-      <c r="AN22" s="15" t="inlineStr"/>
-      <c r="AO22" s="15" t="inlineStr"/>
-      <c r="AP22" s="15" t="inlineStr"/>
-      <c r="AQ22" s="15" t="inlineStr"/>
-      <c r="AR22" s="15" t="inlineStr"/>
-      <c r="AS22" s="15" t="inlineStr"/>
-      <c r="AT22" s="15" t="inlineStr"/>
-      <c r="AU22" s="15" t="inlineStr"/>
-      <c r="AV22" s="15" t="inlineStr"/>
-      <c r="AW22" s="15" t="inlineStr"/>
-      <c r="AX22" s="15" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>crystal-lake</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Crystal Lake</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Bar / cafe / restaurant</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr"/>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Williamsburg</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H23" s="15" t="n">
+      <c r="H23" t="n">
         <v>40.7114</v>
       </c>
-      <c r="I23" s="15" t="n">
+      <c r="I23" t="n">
         <v>-73.9447</v>
       </c>
-      <c r="J23" s="15" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K23" s="15" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L23" s="15" t="inlineStr"/>
-      <c r="M23" s="15" t="inlineStr"/>
-      <c r="N23" s="15" t="inlineStr"/>
-      <c r="O23" s="15" t="inlineStr"/>
-      <c r="P23" s="15" t="inlineStr"/>
-      <c r="Q23" s="15" t="inlineStr"/>
-      <c r="R23" s="15" t="inlineStr"/>
-      <c r="S23" s="15" t="inlineStr"/>
-      <c r="T23" s="15" t="inlineStr"/>
-      <c r="U23" s="15" t="inlineStr"/>
-      <c r="V23" s="15" t="inlineStr"/>
-      <c r="W23" s="15" t="inlineStr"/>
-      <c r="X23" s="15" t="inlineStr"/>
-      <c r="Y23" s="15" t="inlineStr"/>
-      <c r="Z23" s="15" t="inlineStr"/>
-      <c r="AA23" s="15" t="inlineStr"/>
-      <c r="AB23" s="15" t="inlineStr"/>
-      <c r="AC23" s="15" t="inlineStr"/>
-      <c r="AD23" s="15" t="inlineStr"/>
-      <c r="AE23" s="15" t="inlineStr"/>
-      <c r="AF23" s="15" t="inlineStr"/>
-      <c r="AG23" s="15" t="inlineStr"/>
-      <c r="AH23" s="15" t="inlineStr"/>
-      <c r="AI23" s="15" t="inlineStr"/>
-      <c r="AJ23" s="15" t="inlineStr"/>
-      <c r="AK23" s="15" t="inlineStr"/>
-      <c r="AL23" s="15" t="inlineStr"/>
-      <c r="AM23" s="15" t="inlineStr"/>
-      <c r="AN23" s="15" t="inlineStr"/>
-      <c r="AO23" s="15" t="inlineStr"/>
-      <c r="AP23" s="15" t="inlineStr"/>
-      <c r="AQ23" s="15" t="inlineStr"/>
-      <c r="AR23" s="15" t="inlineStr"/>
-      <c r="AS23" s="15" t="inlineStr"/>
-      <c r="AT23" s="15" t="inlineStr"/>
-      <c r="AU23" s="15" t="inlineStr"/>
-      <c r="AV23" s="15" t="inlineStr"/>
-      <c r="AW23" s="15" t="inlineStr"/>
-      <c r="AX23" s="15" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>la-plaza-cultural</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>La Plaza Cultural</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr"/>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H24" s="15" t="n">
+      <c r="H24" t="n">
         <v>40.724</v>
       </c>
-      <c r="I24" s="15" t="n">
+      <c r="I24" t="n">
         <v>-73.9773</v>
       </c>
-      <c r="J24" s="15" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K24" s="15" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L24" s="15" t="inlineStr"/>
-      <c r="M24" s="15" t="inlineStr"/>
-      <c r="N24" s="15" t="inlineStr"/>
-      <c r="O24" s="15" t="inlineStr"/>
-      <c r="P24" s="15" t="inlineStr"/>
-      <c r="Q24" s="15" t="inlineStr"/>
-      <c r="R24" s="15" t="inlineStr"/>
-      <c r="S24" s="15" t="inlineStr"/>
-      <c r="T24" s="15" t="inlineStr"/>
-      <c r="U24" s="15" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V24" s="15" t="inlineStr"/>
-      <c r="W24" s="15" t="inlineStr"/>
-      <c r="X24" s="15" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y24" s="15" t="inlineStr"/>
-      <c r="Z24" s="15" t="inlineStr"/>
-      <c r="AA24" s="15" t="inlineStr"/>
-      <c r="AB24" s="15" t="inlineStr"/>
-      <c r="AC24" s="15" t="inlineStr"/>
-      <c r="AD24" s="15" t="inlineStr"/>
-      <c r="AE24" s="15" t="inlineStr"/>
-      <c r="AF24" s="15" t="inlineStr"/>
-      <c r="AG24" s="15" t="inlineStr"/>
-      <c r="AH24" s="15" t="inlineStr"/>
-      <c r="AI24" s="15" t="inlineStr"/>
-      <c r="AJ24" s="15" t="inlineStr"/>
-      <c r="AK24" s="15" t="inlineStr"/>
-      <c r="AL24" s="15" t="inlineStr"/>
-      <c r="AM24" s="15" t="inlineStr"/>
-      <c r="AN24" s="15" t="inlineStr"/>
-      <c r="AO24" s="15" t="inlineStr"/>
-      <c r="AP24" s="15" t="inlineStr"/>
-      <c r="AQ24" s="15" t="inlineStr"/>
-      <c r="AR24" s="15" t="inlineStr"/>
-      <c r="AS24" s="15" t="inlineStr"/>
-      <c r="AT24" s="15" t="inlineStr"/>
-      <c r="AU24" s="15" t="inlineStr"/>
-      <c r="AV24" s="15" t="inlineStr"/>
-      <c r="AW24" s="15" t="inlineStr"/>
-      <c r="AX24" s="15" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>national-academy-of-design</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>National Academy of Design</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Gallery / museum</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>519 W 26th St, 2nd Fl, New York, NY 10001</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Chelsea</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H25" t="n">
         <v>40.7502</v>
       </c>
-      <c r="I25" s="15" t="n">
+      <c r="I25" t="n">
         <v>-74.0048</v>
       </c>
-      <c r="J25" s="15" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K25" s="15" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L25" s="15" t="inlineStr"/>
-      <c r="M25" s="15" t="inlineStr"/>
-      <c r="N25" s="15" t="inlineStr"/>
-      <c r="O25" s="15" t="inlineStr"/>
-      <c r="P25" s="15" t="inlineStr"/>
-      <c r="Q25" s="15" t="inlineStr"/>
-      <c r="R25" s="15" t="inlineStr"/>
-      <c r="S25" s="15" t="inlineStr"/>
-      <c r="T25" s="15" t="inlineStr"/>
-      <c r="U25" s="15" t="inlineStr"/>
-      <c r="V25" s="15" t="inlineStr"/>
-      <c r="W25" s="15" t="inlineStr"/>
-      <c r="X25" s="15" t="inlineStr"/>
-      <c r="Y25" s="15" t="inlineStr"/>
-      <c r="Z25" s="15" t="inlineStr"/>
-      <c r="AA25" s="15" t="inlineStr"/>
-      <c r="AB25" s="15" t="inlineStr"/>
-      <c r="AC25" s="15" t="inlineStr"/>
-      <c r="AD25" s="15" t="inlineStr"/>
-      <c r="AE25" s="15" t="inlineStr"/>
-      <c r="AF25" s="15" t="inlineStr"/>
-      <c r="AG25" s="15" t="inlineStr"/>
-      <c r="AH25" s="15" t="inlineStr"/>
-      <c r="AI25" s="15" t="inlineStr"/>
-      <c r="AJ25" s="15" t="inlineStr"/>
-      <c r="AK25" s="15" t="inlineStr"/>
-      <c r="AL25" s="15" t="inlineStr"/>
-      <c r="AM25" s="15" t="inlineStr"/>
-      <c r="AN25" s="15" t="inlineStr"/>
-      <c r="AO25" s="15" t="inlineStr"/>
-      <c r="AP25" s="15" t="inlineStr"/>
-      <c r="AQ25" s="15" t="inlineStr"/>
-      <c r="AR25" s="15" t="inlineStr"/>
-      <c r="AS25" s="15" t="inlineStr"/>
-      <c r="AT25" s="15" t="inlineStr"/>
-      <c r="AU25" s="15" t="inlineStr"/>
-      <c r="AV25" s="15" t="inlineStr"/>
-      <c r="AW25" s="15" t="inlineStr"/>
-      <c r="AX25" s="15" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>petes-candy-store</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Pete's Candy Store</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Bar / cafe / restaurant</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr"/>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Williamsburg</t>
         </is>
       </c>
-      <c r="G26" s="15" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H26" s="15" t="n">
+      <c r="H26" t="n">
         <v>40.7182</v>
       </c>
-      <c r="I26" s="15" t="n">
+      <c r="I26" t="n">
         <v>-73.9507</v>
       </c>
-      <c r="J26" s="15" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K26" s="15" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L26" s="15" t="inlineStr"/>
-      <c r="M26" s="15" t="inlineStr"/>
-      <c r="N26" s="15" t="inlineStr"/>
-      <c r="O26" s="15" t="inlineStr"/>
-      <c r="P26" s="15" t="inlineStr"/>
-      <c r="Q26" s="15" t="inlineStr"/>
-      <c r="R26" s="15" t="inlineStr"/>
-      <c r="S26" s="15" t="inlineStr"/>
-      <c r="T26" s="15" t="inlineStr"/>
-      <c r="U26" s="15" t="inlineStr"/>
-      <c r="V26" s="15" t="inlineStr"/>
-      <c r="W26" s="15" t="inlineStr"/>
-      <c r="X26" s="15" t="inlineStr"/>
-      <c r="Y26" s="15" t="inlineStr"/>
-      <c r="Z26" s="15" t="inlineStr"/>
-      <c r="AA26" s="15" t="inlineStr"/>
-      <c r="AB26" s="15" t="inlineStr"/>
-      <c r="AC26" s="15" t="inlineStr"/>
-      <c r="AD26" s="15" t="inlineStr"/>
-      <c r="AE26" s="15" t="inlineStr"/>
-      <c r="AF26" s="15" t="inlineStr"/>
-      <c r="AG26" s="15" t="inlineStr"/>
-      <c r="AH26" s="15" t="inlineStr"/>
-      <c r="AI26" s="15" t="inlineStr"/>
-      <c r="AJ26" s="15" t="inlineStr"/>
-      <c r="AK26" s="15" t="inlineStr"/>
-      <c r="AL26" s="15" t="inlineStr"/>
-      <c r="AM26" s="15" t="inlineStr"/>
-      <c r="AN26" s="15" t="inlineStr"/>
-      <c r="AO26" s="15" t="inlineStr"/>
-      <c r="AP26" s="15" t="inlineStr"/>
-      <c r="AQ26" s="15" t="inlineStr"/>
-      <c r="AR26" s="15" t="inlineStr"/>
-      <c r="AS26" s="15" t="inlineStr"/>
-      <c r="AT26" s="15" t="inlineStr"/>
-      <c r="AU26" s="15" t="inlineStr"/>
-      <c r="AV26" s="15" t="inlineStr"/>
-      <c r="AW26" s="15" t="inlineStr"/>
-      <c r="AX26" s="15" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>53-bridge-st</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>53 Bridge St. (NYC Mesh)</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Community tech space</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>53 Bridge St, Brooklyn, NY 11201</t>
         </is>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>DUMBO</t>
         </is>
       </c>
-      <c r="G27" s="15" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H27" s="15" t="n">
+      <c r="H27" t="n">
         <v>40.7032</v>
       </c>
-      <c r="I27" s="15" t="n">
+      <c r="I27" t="n">
         <v>-73.9845</v>
       </c>
-      <c r="J27" s="15" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K27" s="15" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L27" s="15" t="inlineStr"/>
-      <c r="M27" s="15" t="inlineStr"/>
-      <c r="N27" s="15" t="inlineStr"/>
-      <c r="O27" s="15" t="inlineStr"/>
-      <c r="P27" s="15" t="inlineStr"/>
-      <c r="Q27" s="15" t="inlineStr"/>
-      <c r="R27" s="15" t="inlineStr"/>
-      <c r="S27" s="15" t="inlineStr"/>
-      <c r="T27" s="15" t="inlineStr"/>
-      <c r="U27" s="15" t="inlineStr"/>
-      <c r="V27" s="15" t="inlineStr"/>
-      <c r="W27" s="15" t="inlineStr"/>
-      <c r="X27" s="15" t="inlineStr"/>
-      <c r="Y27" s="15" t="inlineStr"/>
-      <c r="Z27" s="15" t="inlineStr"/>
-      <c r="AA27" s="15" t="inlineStr"/>
-      <c r="AB27" s="15" t="inlineStr"/>
-      <c r="AC27" s="15" t="inlineStr"/>
-      <c r="AD27" s="15" t="inlineStr"/>
-      <c r="AE27" s="15" t="inlineStr"/>
-      <c r="AF27" s="15" t="inlineStr"/>
-      <c r="AG27" s="15" t="inlineStr"/>
-      <c r="AH27" s="15" t="inlineStr"/>
-      <c r="AI27" s="15" t="inlineStr"/>
-      <c r="AJ27" s="15" t="inlineStr"/>
-      <c r="AK27" s="15" t="inlineStr"/>
-      <c r="AL27" s="15" t="inlineStr"/>
-      <c r="AM27" s="15" t="inlineStr"/>
-      <c r="AN27" s="15" t="inlineStr"/>
-      <c r="AO27" s="15" t="inlineStr"/>
-      <c r="AP27" s="15" t="inlineStr"/>
-      <c r="AQ27" s="15" t="inlineStr"/>
-      <c r="AR27" s="15" t="inlineStr"/>
-      <c r="AS27" s="15" t="inlineStr"/>
-      <c r="AT27" s="15" t="inlineStr"/>
-      <c r="AU27" s="15" t="inlineStr"/>
-      <c r="AV27" s="15" t="inlineStr"/>
-      <c r="AW27" s="15" t="inlineStr"/>
-      <c r="AX27" s="15" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>brooklyn-bridge-park</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Brooklyn Bridge Park</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr"/>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>DUMBO / Brooklyn Heights</t>
         </is>
       </c>
-      <c r="G28" s="15" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H28" s="15" t="n">
+      <c r="H28" t="n">
         <v>40.7003</v>
       </c>
-      <c r="I28" s="15" t="n">
+      <c r="I28" t="n">
         <v>-73.9967</v>
       </c>
-      <c r="J28" s="15" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K28" s="15" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L28" s="15" t="inlineStr"/>
-      <c r="M28" s="15" t="inlineStr"/>
-      <c r="N28" s="15" t="inlineStr"/>
-      <c r="O28" s="15" t="inlineStr"/>
-      <c r="P28" s="15" t="inlineStr"/>
-      <c r="Q28" s="15" t="inlineStr"/>
-      <c r="R28" s="15" t="inlineStr"/>
-      <c r="S28" s="15" t="inlineStr"/>
-      <c r="T28" s="15" t="inlineStr"/>
-      <c r="U28" s="15" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V28" s="15" t="inlineStr"/>
-      <c r="W28" s="15" t="inlineStr"/>
-      <c r="X28" s="15" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y28" s="15" t="inlineStr"/>
-      <c r="Z28" s="15" t="inlineStr"/>
-      <c r="AA28" s="15" t="inlineStr"/>
-      <c r="AB28" s="15" t="inlineStr"/>
-      <c r="AC28" s="15" t="inlineStr"/>
-      <c r="AD28" s="15" t="inlineStr"/>
-      <c r="AE28" s="15" t="inlineStr"/>
-      <c r="AF28" s="15" t="inlineStr"/>
-      <c r="AG28" s="15" t="inlineStr"/>
-      <c r="AH28" s="15" t="inlineStr"/>
-      <c r="AI28" s="15" t="inlineStr"/>
-      <c r="AJ28" s="15" t="inlineStr"/>
-      <c r="AK28" s="15" t="inlineStr"/>
-      <c r="AL28" s="15" t="inlineStr"/>
-      <c r="AM28" s="15" t="inlineStr"/>
-      <c r="AN28" s="15" t="inlineStr"/>
-      <c r="AO28" s="15" t="inlineStr"/>
-      <c r="AP28" s="15" t="inlineStr"/>
-      <c r="AQ28" s="15" t="inlineStr"/>
-      <c r="AR28" s="15" t="inlineStr"/>
-      <c r="AS28" s="15" t="inlineStr"/>
-      <c r="AT28" s="15" t="inlineStr"/>
-      <c r="AU28" s="15" t="inlineStr"/>
-      <c r="AV28" s="15" t="inlineStr"/>
-      <c r="AW28" s="15" t="inlineStr"/>
-      <c r="AX28" s="15" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>producers-club</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Producers Club</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Club / event venue</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr"/>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Midtown</t>
         </is>
       </c>
-      <c r="G29" s="15" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H29" s="15" t="n">
+      <c r="H29" t="n">
         <v>40.7593</v>
       </c>
-      <c r="I29" s="15" t="n">
+      <c r="I29" t="n">
         <v>-73.99209999999999</v>
       </c>
-      <c r="J29" s="15" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K29" s="15" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L29" s="15" t="inlineStr"/>
-      <c r="M29" s="15" t="inlineStr"/>
-      <c r="N29" s="15" t="inlineStr"/>
-      <c r="O29" s="15" t="inlineStr"/>
-      <c r="P29" s="15" t="inlineStr"/>
-      <c r="Q29" s="15" t="inlineStr"/>
-      <c r="R29" s="15" t="inlineStr"/>
-      <c r="S29" s="15" t="inlineStr"/>
-      <c r="T29" s="15" t="inlineStr"/>
-      <c r="U29" s="15" t="inlineStr"/>
-      <c r="V29" s="15" t="inlineStr"/>
-      <c r="W29" s="15" t="inlineStr"/>
-      <c r="X29" s="15" t="inlineStr"/>
-      <c r="Y29" s="15" t="inlineStr"/>
-      <c r="Z29" s="15" t="inlineStr"/>
-      <c r="AA29" s="15" t="inlineStr"/>
-      <c r="AB29" s="15" t="inlineStr"/>
-      <c r="AC29" s="15" t="inlineStr"/>
-      <c r="AD29" s="15" t="inlineStr"/>
-      <c r="AE29" s="15" t="inlineStr"/>
-      <c r="AF29" s="15" t="inlineStr"/>
-      <c r="AG29" s="15" t="inlineStr"/>
-      <c r="AH29" s="15" t="inlineStr"/>
-      <c r="AI29" s="15" t="inlineStr"/>
-      <c r="AJ29" s="15" t="inlineStr"/>
-      <c r="AK29" s="15" t="inlineStr"/>
-      <c r="AL29" s="15" t="inlineStr"/>
-      <c r="AM29" s="15" t="inlineStr"/>
-      <c r="AN29" s="15" t="inlineStr"/>
-      <c r="AO29" s="15" t="inlineStr"/>
-      <c r="AP29" s="15" t="inlineStr"/>
-      <c r="AQ29" s="15" t="inlineStr"/>
-      <c r="AR29" s="15" t="inlineStr"/>
-      <c r="AS29" s="15" t="inlineStr"/>
-      <c r="AT29" s="15" t="inlineStr"/>
-      <c r="AU29" s="15" t="inlineStr"/>
-      <c r="AV29" s="15" t="inlineStr"/>
-      <c r="AW29" s="15" t="inlineStr"/>
-      <c r="AX29" s="15" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>the-sultan-room</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>The Sultan Room</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Club / event venue</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr"/>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Bushwick</t>
         </is>
       </c>
-      <c r="G30" s="15" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H30" s="15" t="n">
+      <c r="H30" t="n">
         <v>40.7046</v>
       </c>
-      <c r="I30" s="15" t="n">
+      <c r="I30" t="n">
         <v>-73.9216</v>
       </c>
-      <c r="J30" s="15" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K30" s="15" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="L30" s="15" t="inlineStr"/>
-      <c r="M30" s="15" t="inlineStr"/>
-      <c r="N30" s="15" t="inlineStr"/>
-      <c r="O30" s="15" t="inlineStr"/>
-      <c r="P30" s="15" t="inlineStr"/>
-      <c r="Q30" s="15" t="inlineStr"/>
-      <c r="R30" s="15" t="inlineStr"/>
-      <c r="S30" s="15" t="inlineStr"/>
-      <c r="T30" s="15" t="inlineStr"/>
-      <c r="U30" s="15" t="inlineStr"/>
-      <c r="V30" s="15" t="inlineStr"/>
-      <c r="W30" s="15" t="inlineStr"/>
-      <c r="X30" s="15" t="inlineStr"/>
-      <c r="Y30" s="15" t="inlineStr"/>
-      <c r="Z30" s="15" t="inlineStr"/>
-      <c r="AA30" s="15" t="inlineStr"/>
-      <c r="AB30" s="15" t="inlineStr"/>
-      <c r="AC30" s="15" t="inlineStr"/>
-      <c r="AD30" s="15" t="inlineStr"/>
-      <c r="AE30" s="15" t="inlineStr"/>
-      <c r="AF30" s="15" t="inlineStr"/>
-      <c r="AG30" s="15" t="inlineStr"/>
-      <c r="AH30" s="15" t="inlineStr"/>
-      <c r="AI30" s="15" t="inlineStr"/>
-      <c r="AJ30" s="15" t="inlineStr"/>
-      <c r="AK30" s="15" t="inlineStr"/>
-      <c r="AL30" s="15" t="inlineStr"/>
-      <c r="AM30" s="15" t="inlineStr"/>
-      <c r="AN30" s="15" t="inlineStr"/>
-      <c r="AO30" s="15" t="inlineStr"/>
-      <c r="AP30" s="15" t="inlineStr"/>
-      <c r="AQ30" s="15" t="inlineStr"/>
-      <c r="AR30" s="15" t="inlineStr"/>
-      <c r="AS30" s="15" t="inlineStr"/>
-      <c r="AT30" s="15" t="inlineStr"/>
-      <c r="AU30" s="15" t="inlineStr"/>
-      <c r="AV30" s="15" t="inlineStr"/>
-      <c r="AW30" s="15" t="inlineStr"/>
-      <c r="AX30" s="15" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>underland-gallery</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Underland Gallery</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Gallery / museum</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr"/>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Bay Ridge</t>
         </is>
       </c>
-      <c r="G31" s="15" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H31" s="15" t="n">
+      <c r="H31" t="n">
         <v>40.63</v>
       </c>
-      <c r="I31" s="15" t="n">
+      <c r="I31" t="n">
         <v>-74.027</v>
       </c>
-      <c r="J31" s="15" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>approx</t>
         </is>
       </c>
-      <c r="K31" s="15" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L31" s="15" t="inlineStr"/>
-      <c r="M31" s="15" t="inlineStr"/>
-      <c r="N31" s="15" t="inlineStr"/>
-      <c r="O31" s="15" t="inlineStr"/>
-      <c r="P31" s="15" t="inlineStr"/>
-      <c r="Q31" s="15" t="inlineStr"/>
-      <c r="R31" s="15" t="inlineStr"/>
-      <c r="S31" s="15" t="inlineStr"/>
-      <c r="T31" s="15" t="inlineStr"/>
-      <c r="U31" s="15" t="inlineStr"/>
-      <c r="V31" s="15" t="inlineStr"/>
-      <c r="W31" s="15" t="inlineStr"/>
-      <c r="X31" s="15" t="inlineStr"/>
-      <c r="Y31" s="15" t="inlineStr"/>
-      <c r="Z31" s="15" t="inlineStr"/>
-      <c r="AA31" s="15" t="inlineStr"/>
-      <c r="AB31" s="15" t="inlineStr"/>
-      <c r="AC31" s="15" t="inlineStr"/>
-      <c r="AD31" s="15" t="inlineStr"/>
-      <c r="AE31" s="15" t="inlineStr"/>
-      <c r="AF31" s="15" t="inlineStr"/>
-      <c r="AG31" s="15" t="inlineStr"/>
-      <c r="AH31" s="15" t="inlineStr"/>
-      <c r="AI31" s="15" t="inlineStr"/>
-      <c r="AJ31" s="15" t="inlineStr"/>
-      <c r="AK31" s="15" t="inlineStr"/>
-      <c r="AL31" s="15" t="inlineStr"/>
-      <c r="AM31" s="15" t="inlineStr"/>
-      <c r="AN31" s="15" t="inlineStr"/>
-      <c r="AO31" s="15" t="inlineStr"/>
-      <c r="AP31" s="15" t="inlineStr"/>
-      <c r="AQ31" s="15" t="inlineStr"/>
-      <c r="AR31" s="15" t="inlineStr"/>
-      <c r="AS31" s="15" t="inlineStr"/>
-      <c r="AT31" s="15" t="inlineStr"/>
-      <c r="AU31" s="15" t="inlineStr"/>
-      <c r="AV31" s="15" t="inlineStr"/>
-      <c r="AW31" s="15" t="inlineStr"/>
-      <c r="AX31" s="15" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>bric</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>BRIC</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr"/>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Fort Greene</t>
         </is>
       </c>
-      <c r="G32" s="15" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H32" s="15" t="n">
+      <c r="H32" t="n">
         <v>40.6871</v>
       </c>
-      <c r="I32" s="15" t="n">
+      <c r="I32" t="n">
         <v>-73.97799999999999</v>
       </c>
-      <c r="J32" s="15" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K32" s="15" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L32" s="15" t="inlineStr"/>
-      <c r="M32" s="15" t="inlineStr"/>
-      <c r="N32" s="15" t="inlineStr"/>
-      <c r="O32" s="15" t="inlineStr"/>
-      <c r="P32" s="15" t="inlineStr"/>
-      <c r="Q32" s="15" t="inlineStr"/>
-      <c r="R32" s="15" t="inlineStr"/>
-      <c r="S32" s="15" t="inlineStr"/>
-      <c r="T32" s="15" t="inlineStr"/>
-      <c r="U32" s="15" t="inlineStr"/>
-      <c r="V32" s="15" t="inlineStr"/>
-      <c r="W32" s="15" t="inlineStr"/>
-      <c r="X32" s="15" t="inlineStr"/>
-      <c r="Y32" s="15" t="inlineStr"/>
-      <c r="Z32" s="15" t="inlineStr"/>
-      <c r="AA32" s="15" t="inlineStr"/>
-      <c r="AB32" s="15" t="inlineStr"/>
-      <c r="AC32" s="15" t="inlineStr"/>
-      <c r="AD32" s="15" t="inlineStr"/>
-      <c r="AE32" s="15" t="inlineStr"/>
-      <c r="AF32" s="15" t="inlineStr"/>
-      <c r="AG32" s="15" t="inlineStr"/>
-      <c r="AH32" s="15" t="inlineStr"/>
-      <c r="AI32" s="15" t="inlineStr"/>
-      <c r="AJ32" s="15" t="inlineStr"/>
-      <c r="AK32" s="15" t="inlineStr"/>
-      <c r="AL32" s="15" t="inlineStr"/>
-      <c r="AM32" s="15" t="inlineStr"/>
-      <c r="AN32" s="15" t="inlineStr"/>
-      <c r="AO32" s="15" t="inlineStr"/>
-      <c r="AP32" s="15" t="inlineStr"/>
-      <c r="AQ32" s="15" t="inlineStr"/>
-      <c r="AR32" s="15" t="inlineStr"/>
-      <c r="AS32" s="15" t="inlineStr"/>
-      <c r="AT32" s="15" t="inlineStr"/>
-      <c r="AU32" s="15" t="inlineStr"/>
-      <c r="AV32" s="15" t="inlineStr"/>
-      <c r="AW32" s="15" t="inlineStr"/>
-      <c r="AX32" s="15" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>church-of-the-village</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Church of the Village</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Church / meeting house</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr"/>
-      <c r="F33" s="15" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>West Village</t>
         </is>
       </c>
-      <c r="G33" s="15" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H33" s="15" t="n">
+      <c r="H33" t="n">
         <v>40.7377</v>
       </c>
-      <c r="I33" s="15" t="n">
+      <c r="I33" t="n">
         <v>-74.00149999999999</v>
       </c>
-      <c r="J33" s="15" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K33" s="15" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L33" s="15" t="inlineStr"/>
-      <c r="M33" s="15" t="inlineStr"/>
-      <c r="N33" s="15" t="inlineStr"/>
-      <c r="O33" s="15" t="inlineStr"/>
-      <c r="P33" s="15" t="inlineStr"/>
-      <c r="Q33" s="15" t="inlineStr"/>
-      <c r="R33" s="15" t="inlineStr"/>
-      <c r="S33" s="15" t="inlineStr"/>
-      <c r="T33" s="15" t="inlineStr"/>
-      <c r="U33" s="15" t="inlineStr"/>
-      <c r="V33" s="15" t="inlineStr"/>
-      <c r="W33" s="15" t="inlineStr"/>
-      <c r="X33" s="15" t="inlineStr"/>
-      <c r="Y33" s="15" t="inlineStr"/>
-      <c r="Z33" s="15" t="inlineStr"/>
-      <c r="AA33" s="15" t="inlineStr"/>
-      <c r="AB33" s="15" t="inlineStr"/>
-      <c r="AC33" s="15" t="inlineStr"/>
-      <c r="AD33" s="15" t="inlineStr"/>
-      <c r="AE33" s="15" t="inlineStr"/>
-      <c r="AF33" s="15" t="inlineStr"/>
-      <c r="AG33" s="15" t="inlineStr"/>
-      <c r="AH33" s="15" t="inlineStr"/>
-      <c r="AI33" s="15" t="inlineStr"/>
-      <c r="AJ33" s="15" t="inlineStr"/>
-      <c r="AK33" s="15" t="inlineStr"/>
-      <c r="AL33" s="15" t="inlineStr"/>
-      <c r="AM33" s="15" t="inlineStr"/>
-      <c r="AN33" s="15" t="inlineStr"/>
-      <c r="AO33" s="15" t="inlineStr"/>
-      <c r="AP33" s="15" t="inlineStr"/>
-      <c r="AQ33" s="15" t="inlineStr"/>
-      <c r="AR33" s="15" t="inlineStr"/>
-      <c r="AS33" s="15" t="inlineStr"/>
-      <c r="AT33" s="15" t="inlineStr"/>
-      <c r="AU33" s="15" t="inlineStr"/>
-      <c r="AV33" s="15" t="inlineStr"/>
-      <c r="AW33" s="15" t="inlineStr"/>
-      <c r="AX33" s="15" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>index-chinatown</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Index Chinatown</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr"/>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Chinatown</t>
         </is>
       </c>
-      <c r="G34" s="15" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H34" s="15" t="n">
+      <c r="H34" t="n">
         <v>40.7155</v>
       </c>
-      <c r="I34" s="15" t="n">
+      <c r="I34" t="n">
         <v>-73.997</v>
       </c>
-      <c r="J34" s="15" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>approx</t>
         </is>
       </c>
-      <c r="K34" s="15" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L34" s="15" t="inlineStr"/>
-      <c r="M34" s="15" t="inlineStr"/>
-      <c r="N34" s="15" t="inlineStr"/>
-      <c r="O34" s="15" t="inlineStr"/>
-      <c r="P34" s="15" t="inlineStr"/>
-      <c r="Q34" s="15" t="inlineStr"/>
-      <c r="R34" s="15" t="inlineStr"/>
-      <c r="S34" s="15" t="inlineStr"/>
-      <c r="T34" s="15" t="inlineStr"/>
-      <c r="U34" s="15" t="inlineStr"/>
-      <c r="V34" s="15" t="inlineStr"/>
-      <c r="W34" s="15" t="inlineStr"/>
-      <c r="X34" s="15" t="inlineStr"/>
-      <c r="Y34" s="15" t="inlineStr"/>
-      <c r="Z34" s="15" t="inlineStr"/>
-      <c r="AA34" s="15" t="inlineStr"/>
-      <c r="AB34" s="15" t="inlineStr"/>
-      <c r="AC34" s="15" t="inlineStr"/>
-      <c r="AD34" s="15" t="inlineStr"/>
-      <c r="AE34" s="15" t="inlineStr"/>
-      <c r="AF34" s="15" t="inlineStr"/>
-      <c r="AG34" s="15" t="inlineStr"/>
-      <c r="AH34" s="15" t="inlineStr"/>
-      <c r="AI34" s="15" t="inlineStr"/>
-      <c r="AJ34" s="15" t="inlineStr"/>
-      <c r="AK34" s="15" t="inlineStr"/>
-      <c r="AL34" s="15" t="inlineStr"/>
-      <c r="AM34" s="15" t="inlineStr"/>
-      <c r="AN34" s="15" t="inlineStr"/>
-      <c r="AO34" s="15" t="inlineStr"/>
-      <c r="AP34" s="15" t="inlineStr"/>
-      <c r="AQ34" s="15" t="inlineStr"/>
-      <c r="AR34" s="15" t="inlineStr"/>
-      <c r="AS34" s="15" t="inlineStr"/>
-      <c r="AT34" s="15" t="inlineStr"/>
-      <c r="AU34" s="15" t="inlineStr"/>
-      <c r="AV34" s="15" t="inlineStr"/>
-      <c r="AW34" s="15" t="inlineStr"/>
-      <c r="AX34" s="15" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>interference-archive</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Interference Archive</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr"/>
-      <c r="F35" s="15" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Gowanus</t>
         </is>
       </c>
-      <c r="G35" s="15" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H35" t="n">
         <v>40.6712</v>
       </c>
-      <c r="I35" s="15" t="n">
+      <c r="I35" t="n">
         <v>-73.98350000000001</v>
       </c>
-      <c r="J35" s="15" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K35" s="15" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L35" s="15" t="inlineStr"/>
-      <c r="M35" s="15" t="inlineStr"/>
-      <c r="N35" s="15" t="inlineStr"/>
-      <c r="O35" s="15" t="inlineStr"/>
-      <c r="P35" s="15" t="inlineStr"/>
-      <c r="Q35" s="15" t="inlineStr"/>
-      <c r="R35" s="15" t="inlineStr"/>
-      <c r="S35" s="15" t="inlineStr"/>
-      <c r="T35" s="15" t="inlineStr"/>
-      <c r="U35" s="15" t="inlineStr"/>
-      <c r="V35" s="15" t="inlineStr"/>
-      <c r="W35" s="15" t="inlineStr"/>
-      <c r="X35" s="15" t="inlineStr"/>
-      <c r="Y35" s="15" t="inlineStr"/>
-      <c r="Z35" s="15" t="inlineStr"/>
-      <c r="AA35" s="15" t="inlineStr"/>
-      <c r="AB35" s="15" t="inlineStr"/>
-      <c r="AC35" s="15" t="inlineStr"/>
-      <c r="AD35" s="15" t="inlineStr"/>
-      <c r="AE35" s="15" t="inlineStr"/>
-      <c r="AF35" s="15" t="inlineStr"/>
-      <c r="AG35" s="15" t="inlineStr"/>
-      <c r="AH35" s="15" t="inlineStr"/>
-      <c r="AI35" s="15" t="inlineStr"/>
-      <c r="AJ35" s="15" t="inlineStr"/>
-      <c r="AK35" s="15" t="inlineStr"/>
-      <c r="AL35" s="15" t="inlineStr"/>
-      <c r="AM35" s="15" t="inlineStr"/>
-      <c r="AN35" s="15" t="inlineStr"/>
-      <c r="AO35" s="15" t="inlineStr"/>
-      <c r="AP35" s="15" t="inlineStr"/>
-      <c r="AQ35" s="15" t="inlineStr"/>
-      <c r="AR35" s="15" t="inlineStr"/>
-      <c r="AS35" s="15" t="inlineStr"/>
-      <c r="AT35" s="15" t="inlineStr"/>
-      <c r="AU35" s="15" t="inlineStr"/>
-      <c r="AV35" s="15" t="inlineStr"/>
-      <c r="AW35" s="15" t="inlineStr"/>
-      <c r="AX35" s="15" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>jade</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>JADE</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Club / event venue</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>4 Stuyvesant Ave, Brooklyn, NY 11221</t>
         </is>
       </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Bushwick</t>
         </is>
       </c>
-      <c r="G36" s="15" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H36" s="15" t="n">
+      <c r="H36" t="n">
         <v>40.6977</v>
       </c>
-      <c r="I36" s="15" t="n">
+      <c r="I36" t="n">
         <v>-73.9366</v>
       </c>
-      <c r="J36" s="15" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K36" s="15" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L36" s="15" t="inlineStr"/>
-      <c r="M36" s="15" t="inlineStr"/>
-      <c r="N36" s="15" t="inlineStr"/>
-      <c r="O36" s="15" t="inlineStr"/>
-      <c r="P36" s="15" t="inlineStr"/>
-      <c r="Q36" s="15" t="inlineStr"/>
-      <c r="R36" s="15" t="inlineStr"/>
-      <c r="S36" s="15" t="inlineStr"/>
-      <c r="T36" s="15" t="inlineStr"/>
-      <c r="U36" s="15" t="inlineStr"/>
-      <c r="V36" s="15" t="inlineStr"/>
-      <c r="W36" s="15" t="inlineStr"/>
-      <c r="X36" s="15" t="inlineStr"/>
-      <c r="Y36" s="15" t="inlineStr"/>
-      <c r="Z36" s="15" t="inlineStr"/>
-      <c r="AA36" s="15" t="inlineStr"/>
-      <c r="AB36" s="15" t="inlineStr"/>
-      <c r="AC36" s="15" t="inlineStr"/>
-      <c r="AD36" s="15" t="inlineStr"/>
-      <c r="AE36" s="15" t="inlineStr"/>
-      <c r="AF36" s="15" t="inlineStr"/>
-      <c r="AG36" s="15" t="inlineStr"/>
-      <c r="AH36" s="15" t="inlineStr"/>
-      <c r="AI36" s="15" t="inlineStr"/>
-      <c r="AJ36" s="15" t="inlineStr"/>
-      <c r="AK36" s="15" t="inlineStr"/>
-      <c r="AL36" s="15" t="inlineStr"/>
-      <c r="AM36" s="15" t="inlineStr"/>
-      <c r="AN36" s="15" t="inlineStr"/>
-      <c r="AO36" s="15" t="inlineStr"/>
-      <c r="AP36" s="15" t="inlineStr"/>
-      <c r="AQ36" s="15" t="inlineStr"/>
-      <c r="AR36" s="15" t="inlineStr"/>
-      <c r="AS36" s="15" t="inlineStr"/>
-      <c r="AT36" s="15" t="inlineStr"/>
-      <c r="AU36" s="15" t="inlineStr"/>
-      <c r="AV36" s="15" t="inlineStr"/>
-      <c r="AW36" s="15" t="inlineStr"/>
-      <c r="AX36" s="15" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>madison-square-park</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Madison Square Park</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr"/>
-      <c r="F37" s="15" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Flatiron</t>
         </is>
       </c>
-      <c r="G37" s="15" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H37" s="15" t="n">
+      <c r="H37" t="n">
         <v>40.742</v>
       </c>
-      <c r="I37" s="15" t="n">
+      <c r="I37" t="n">
         <v>-73.9875</v>
       </c>
-      <c r="J37" s="15" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K37" s="15" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L37" s="15" t="inlineStr"/>
-      <c r="M37" s="15" t="inlineStr"/>
-      <c r="N37" s="15" t="inlineStr"/>
-      <c r="O37" s="15" t="inlineStr"/>
-      <c r="P37" s="15" t="inlineStr"/>
-      <c r="Q37" s="15" t="inlineStr"/>
-      <c r="R37" s="15" t="inlineStr"/>
-      <c r="S37" s="15" t="inlineStr"/>
-      <c r="T37" s="15" t="inlineStr"/>
-      <c r="U37" s="15" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V37" s="15" t="inlineStr"/>
-      <c r="W37" s="15" t="inlineStr"/>
-      <c r="X37" s="15" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y37" s="15" t="inlineStr"/>
-      <c r="Z37" s="15" t="inlineStr"/>
-      <c r="AA37" s="15" t="inlineStr"/>
-      <c r="AB37" s="15" t="inlineStr"/>
-      <c r="AC37" s="15" t="inlineStr"/>
-      <c r="AD37" s="15" t="inlineStr"/>
-      <c r="AE37" s="15" t="inlineStr"/>
-      <c r="AF37" s="15" t="inlineStr"/>
-      <c r="AG37" s="15" t="inlineStr"/>
-      <c r="AH37" s="15" t="inlineStr"/>
-      <c r="AI37" s="15" t="inlineStr"/>
-      <c r="AJ37" s="15" t="inlineStr"/>
-      <c r="AK37" s="15" t="inlineStr"/>
-      <c r="AL37" s="15" t="inlineStr"/>
-      <c r="AM37" s="15" t="inlineStr"/>
-      <c r="AN37" s="15" t="inlineStr"/>
-      <c r="AO37" s="15" t="inlineStr"/>
-      <c r="AP37" s="15" t="inlineStr"/>
-      <c r="AQ37" s="15" t="inlineStr"/>
-      <c r="AR37" s="15" t="inlineStr"/>
-      <c r="AS37" s="15" t="inlineStr"/>
-      <c r="AT37" s="15" t="inlineStr"/>
-      <c r="AU37" s="15" t="inlineStr"/>
-      <c r="AV37" s="15" t="inlineStr"/>
-      <c r="AW37" s="15" t="inlineStr"/>
-      <c r="AX37" s="15" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>mcgolrick-park</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>McGolrick Park</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr"/>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Greenpoint</t>
         </is>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H38" s="15" t="n">
+      <c r="H38" t="n">
         <v>40.7246</v>
       </c>
-      <c r="I38" s="15" t="n">
+      <c r="I38" t="n">
         <v>-73.9434</v>
       </c>
-      <c r="J38" s="15" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K38" s="15" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L38" s="15" t="inlineStr"/>
-      <c r="M38" s="15" t="inlineStr"/>
-      <c r="N38" s="15" t="inlineStr"/>
-      <c r="O38" s="15" t="inlineStr"/>
-      <c r="P38" s="15" t="inlineStr"/>
-      <c r="Q38" s="15" t="inlineStr"/>
-      <c r="R38" s="15" t="inlineStr"/>
-      <c r="S38" s="15" t="inlineStr"/>
-      <c r="T38" s="15" t="inlineStr"/>
-      <c r="U38" s="15" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V38" s="15" t="inlineStr"/>
-      <c r="W38" s="15" t="inlineStr"/>
-      <c r="X38" s="15" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y38" s="15" t="inlineStr"/>
-      <c r="Z38" s="15" t="inlineStr"/>
-      <c r="AA38" s="15" t="inlineStr"/>
-      <c r="AB38" s="15" t="inlineStr"/>
-      <c r="AC38" s="15" t="inlineStr"/>
-      <c r="AD38" s="15" t="inlineStr"/>
-      <c r="AE38" s="15" t="inlineStr"/>
-      <c r="AF38" s="15" t="inlineStr"/>
-      <c r="AG38" s="15" t="inlineStr"/>
-      <c r="AH38" s="15" t="inlineStr"/>
-      <c r="AI38" s="15" t="inlineStr"/>
-      <c r="AJ38" s="15" t="inlineStr"/>
-      <c r="AK38" s="15" t="inlineStr"/>
-      <c r="AL38" s="15" t="inlineStr"/>
-      <c r="AM38" s="15" t="inlineStr"/>
-      <c r="AN38" s="15" t="inlineStr"/>
-      <c r="AO38" s="15" t="inlineStr"/>
-      <c r="AP38" s="15" t="inlineStr"/>
-      <c r="AQ38" s="15" t="inlineStr"/>
-      <c r="AR38" s="15" t="inlineStr"/>
-      <c r="AS38" s="15" t="inlineStr"/>
-      <c r="AT38" s="15" t="inlineStr"/>
-      <c r="AU38" s="15" t="inlineStr"/>
-      <c r="AV38" s="15" t="inlineStr"/>
-      <c r="AW38" s="15" t="inlineStr"/>
-      <c r="AX38" s="15" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>metrorock-bushwick</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>MetroRock Bushwick</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Club / event venue</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr"/>
-      <c r="F39" s="15" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Bushwick</t>
         </is>
       </c>
-      <c r="G39" s="15" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H39" s="15" t="n">
+      <c r="H39" t="n">
         <v>40.7059</v>
       </c>
-      <c r="I39" s="15" t="n">
+      <c r="I39" t="n">
         <v>-73.9196</v>
       </c>
-      <c r="J39" s="15" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K39" s="15" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L39" s="15" t="inlineStr"/>
-      <c r="M39" s="15" t="inlineStr"/>
-      <c r="N39" s="15" t="inlineStr"/>
-      <c r="O39" s="15" t="inlineStr"/>
-      <c r="P39" s="15" t="inlineStr"/>
-      <c r="Q39" s="15" t="inlineStr"/>
-      <c r="R39" s="15" t="inlineStr"/>
-      <c r="S39" s="15" t="inlineStr"/>
-      <c r="T39" s="15" t="inlineStr"/>
-      <c r="U39" s="15" t="inlineStr"/>
-      <c r="V39" s="15" t="inlineStr"/>
-      <c r="W39" s="15" t="inlineStr"/>
-      <c r="X39" s="15" t="inlineStr"/>
-      <c r="Y39" s="15" t="inlineStr"/>
-      <c r="Z39" s="15" t="inlineStr"/>
-      <c r="AA39" s="15" t="inlineStr"/>
-      <c r="AB39" s="15" t="inlineStr"/>
-      <c r="AC39" s="15" t="inlineStr"/>
-      <c r="AD39" s="15" t="inlineStr"/>
-      <c r="AE39" s="15" t="inlineStr"/>
-      <c r="AF39" s="15" t="inlineStr"/>
-      <c r="AG39" s="15" t="inlineStr"/>
-      <c r="AH39" s="15" t="inlineStr"/>
-      <c r="AI39" s="15" t="inlineStr"/>
-      <c r="AJ39" s="15" t="inlineStr"/>
-      <c r="AK39" s="15" t="inlineStr"/>
-      <c r="AL39" s="15" t="inlineStr"/>
-      <c r="AM39" s="15" t="inlineStr"/>
-      <c r="AN39" s="15" t="inlineStr"/>
-      <c r="AO39" s="15" t="inlineStr"/>
-      <c r="AP39" s="15" t="inlineStr"/>
-      <c r="AQ39" s="15" t="inlineStr"/>
-      <c r="AR39" s="15" t="inlineStr"/>
-      <c r="AS39" s="15" t="inlineStr"/>
-      <c r="AT39" s="15" t="inlineStr"/>
-      <c r="AU39" s="15" t="inlineStr"/>
-      <c r="AV39" s="15" t="inlineStr"/>
-      <c r="AW39" s="15" t="inlineStr"/>
-      <c r="AX39" s="15" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>museum-of-the-moving-image</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Museum of the Moving Image</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Gallery / museum</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr"/>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Astoria</t>
         </is>
       </c>
-      <c r="G40" s="15" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Queens</t>
         </is>
       </c>
-      <c r="H40" s="15" t="n">
+      <c r="H40" t="n">
         <v>40.7563</v>
       </c>
-      <c r="I40" s="15" t="n">
+      <c r="I40" t="n">
         <v>-73.9239</v>
       </c>
-      <c r="J40" s="15" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K40" s="15" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L40" s="15" t="inlineStr"/>
-      <c r="M40" s="15" t="inlineStr"/>
-      <c r="N40" s="15" t="inlineStr"/>
-      <c r="O40" s="15" t="inlineStr"/>
-      <c r="P40" s="15" t="inlineStr"/>
-      <c r="Q40" s="15" t="inlineStr"/>
-      <c r="R40" s="15" t="inlineStr"/>
-      <c r="S40" s="15" t="inlineStr"/>
-      <c r="T40" s="15" t="inlineStr"/>
-      <c r="U40" s="15" t="inlineStr"/>
-      <c r="V40" s="15" t="inlineStr"/>
-      <c r="W40" s="15" t="inlineStr"/>
-      <c r="X40" s="15" t="inlineStr"/>
-      <c r="Y40" s="15" t="inlineStr"/>
-      <c r="Z40" s="15" t="inlineStr"/>
-      <c r="AA40" s="15" t="inlineStr"/>
-      <c r="AB40" s="15" t="inlineStr"/>
-      <c r="AC40" s="15" t="inlineStr"/>
-      <c r="AD40" s="15" t="inlineStr"/>
-      <c r="AE40" s="15" t="inlineStr"/>
-      <c r="AF40" s="15" t="inlineStr"/>
-      <c r="AG40" s="15" t="inlineStr"/>
-      <c r="AH40" s="15" t="inlineStr"/>
-      <c r="AI40" s="15" t="inlineStr"/>
-      <c r="AJ40" s="15" t="inlineStr"/>
-      <c r="AK40" s="15" t="inlineStr"/>
-      <c r="AL40" s="15" t="inlineStr"/>
-      <c r="AM40" s="15" t="inlineStr"/>
-      <c r="AN40" s="15" t="inlineStr"/>
-      <c r="AO40" s="15" t="inlineStr"/>
-      <c r="AP40" s="15" t="inlineStr"/>
-      <c r="AQ40" s="15" t="inlineStr"/>
-      <c r="AR40" s="15" t="inlineStr"/>
-      <c r="AS40" s="15" t="inlineStr"/>
-      <c r="AT40" s="15" t="inlineStr"/>
-      <c r="AU40" s="15" t="inlineStr"/>
-      <c r="AV40" s="15" t="inlineStr"/>
-      <c r="AW40" s="15" t="inlineStr"/>
-      <c r="AX40" s="15" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>nyu-school-of-law-vanderbilt-hall</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>NYU School of Law – Vanderbilt Hall</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>University</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr"/>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Greenwich Village</t>
         </is>
       </c>
-      <c r="G41" s="15" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H41" s="15" t="n">
+      <c r="H41" t="n">
         <v>40.7302</v>
       </c>
-      <c r="I41" s="15" t="n">
+      <c r="I41" t="n">
         <v>-73.99930000000001</v>
       </c>
-      <c r="J41" s="15" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K41" s="15" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L41" s="15" t="inlineStr"/>
-      <c r="M41" s="15" t="inlineStr"/>
-      <c r="N41" s="15" t="inlineStr"/>
-      <c r="O41" s="15" t="inlineStr"/>
-      <c r="P41" s="15" t="inlineStr"/>
-      <c r="Q41" s="15" t="inlineStr"/>
-      <c r="R41" s="15" t="inlineStr"/>
-      <c r="S41" s="15" t="inlineStr"/>
-      <c r="T41" s="15" t="inlineStr"/>
-      <c r="U41" s="15" t="inlineStr"/>
-      <c r="V41" s="15" t="inlineStr"/>
-      <c r="W41" s="15" t="inlineStr"/>
-      <c r="X41" s="15" t="inlineStr"/>
-      <c r="Y41" s="15" t="inlineStr"/>
-      <c r="Z41" s="15" t="inlineStr"/>
-      <c r="AA41" s="15" t="inlineStr"/>
-      <c r="AB41" s="15" t="inlineStr"/>
-      <c r="AC41" s="15" t="inlineStr"/>
-      <c r="AD41" s="15" t="inlineStr"/>
-      <c r="AE41" s="15" t="inlineStr"/>
-      <c r="AF41" s="15" t="inlineStr"/>
-      <c r="AG41" s="15" t="inlineStr"/>
-      <c r="AH41" s="15" t="inlineStr"/>
-      <c r="AI41" s="15" t="inlineStr"/>
-      <c r="AJ41" s="15" t="inlineStr"/>
-      <c r="AK41" s="15" t="inlineStr"/>
-      <c r="AL41" s="15" t="inlineStr"/>
-      <c r="AM41" s="15" t="inlineStr"/>
-      <c r="AN41" s="15" t="inlineStr"/>
-      <c r="AO41" s="15" t="inlineStr"/>
-      <c r="AP41" s="15" t="inlineStr"/>
-      <c r="AQ41" s="15" t="inlineStr"/>
-      <c r="AR41" s="15" t="inlineStr"/>
-      <c r="AS41" s="15" t="inlineStr"/>
-      <c r="AT41" s="15" t="inlineStr"/>
-      <c r="AU41" s="15" t="inlineStr"/>
-      <c r="AV41" s="15" t="inlineStr"/>
-      <c r="AW41" s="15" t="inlineStr"/>
-      <c r="AX41" s="15" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>nightclub-101</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Nightclub 101</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Club / event venue</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>101 Avenue A, New York, NY 10009</t>
         </is>
       </c>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>East Village</t>
         </is>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H42" s="15" t="n">
+      <c r="H42" t="n">
         <v>40.7262</v>
       </c>
-      <c r="I42" s="15" t="n">
+      <c r="I42" t="n">
         <v>-73.98390000000001</v>
       </c>
-      <c r="J42" s="15" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K42" s="15" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L42" s="15" t="inlineStr"/>
-      <c r="M42" s="15" t="inlineStr"/>
-      <c r="N42" s="15" t="inlineStr"/>
-      <c r="O42" s="15" t="inlineStr"/>
-      <c r="P42" s="15" t="inlineStr"/>
-      <c r="Q42" s="15" t="inlineStr"/>
-      <c r="R42" s="15" t="inlineStr"/>
-      <c r="S42" s="15" t="inlineStr"/>
-      <c r="T42" s="15" t="inlineStr"/>
-      <c r="U42" s="15" t="inlineStr"/>
-      <c r="V42" s="15" t="inlineStr"/>
-      <c r="W42" s="15" t="inlineStr"/>
-      <c r="X42" s="15" t="inlineStr"/>
-      <c r="Y42" s="15" t="inlineStr"/>
-      <c r="Z42" s="15" t="inlineStr"/>
-      <c r="AA42" s="15" t="inlineStr"/>
-      <c r="AB42" s="15" t="inlineStr"/>
-      <c r="AC42" s="15" t="inlineStr"/>
-      <c r="AD42" s="15" t="inlineStr"/>
-      <c r="AE42" s="15" t="inlineStr"/>
-      <c r="AF42" s="15" t="inlineStr"/>
-      <c r="AG42" s="15" t="inlineStr"/>
-      <c r="AH42" s="15" t="inlineStr"/>
-      <c r="AI42" s="15" t="inlineStr"/>
-      <c r="AJ42" s="15" t="inlineStr"/>
-      <c r="AK42" s="15" t="inlineStr"/>
-      <c r="AL42" s="15" t="inlineStr"/>
-      <c r="AM42" s="15" t="inlineStr"/>
-      <c r="AN42" s="15" t="inlineStr"/>
-      <c r="AO42" s="15" t="inlineStr"/>
-      <c r="AP42" s="15" t="inlineStr"/>
-      <c r="AQ42" s="15" t="inlineStr"/>
-      <c r="AR42" s="15" t="inlineStr"/>
-      <c r="AS42" s="15" t="inlineStr"/>
-      <c r="AT42" s="15" t="inlineStr"/>
-      <c r="AU42" s="15" t="inlineStr"/>
-      <c r="AV42" s="15" t="inlineStr"/>
-      <c r="AW42" s="15" t="inlineStr"/>
-      <c r="AX42" s="15" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>peace-cafe</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Peace Cafe</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Bar / cafe / restaurant</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>23 Marcus Garvey Blvd, Brooklyn, NY</t>
         </is>
       </c>
-      <c r="F43" s="15" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Bed-Stuy</t>
         </is>
       </c>
-      <c r="G43" s="15" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H43" s="15" t="n">
+      <c r="H43" t="n">
         <v>40.6993</v>
       </c>
-      <c r="I43" s="15" t="n">
+      <c r="I43" t="n">
         <v>-73.9406</v>
       </c>
-      <c r="J43" s="15" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K43" s="15" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L43" s="15" t="inlineStr"/>
-      <c r="M43" s="15" t="inlineStr"/>
-      <c r="N43" s="15" t="inlineStr"/>
-      <c r="O43" s="15" t="inlineStr"/>
-      <c r="P43" s="15" t="inlineStr"/>
-      <c r="Q43" s="15" t="inlineStr"/>
-      <c r="R43" s="15" t="inlineStr"/>
-      <c r="S43" s="15" t="inlineStr"/>
-      <c r="T43" s="15" t="inlineStr"/>
-      <c r="U43" s="15" t="inlineStr"/>
-      <c r="V43" s="15" t="inlineStr"/>
-      <c r="W43" s="15" t="inlineStr"/>
-      <c r="X43" s="15" t="inlineStr"/>
-      <c r="Y43" s="15" t="inlineStr"/>
-      <c r="Z43" s="15" t="inlineStr"/>
-      <c r="AA43" s="15" t="inlineStr"/>
-      <c r="AB43" s="15" t="inlineStr"/>
-      <c r="AC43" s="15" t="inlineStr"/>
-      <c r="AD43" s="15" t="inlineStr"/>
-      <c r="AE43" s="15" t="inlineStr"/>
-      <c r="AF43" s="15" t="inlineStr"/>
-      <c r="AG43" s="15" t="inlineStr"/>
-      <c r="AH43" s="15" t="inlineStr"/>
-      <c r="AI43" s="15" t="inlineStr"/>
-      <c r="AJ43" s="15" t="inlineStr"/>
-      <c r="AK43" s="15" t="inlineStr"/>
-      <c r="AL43" s="15" t="inlineStr"/>
-      <c r="AM43" s="15" t="inlineStr"/>
-      <c r="AN43" s="15" t="inlineStr"/>
-      <c r="AO43" s="15" t="inlineStr"/>
-      <c r="AP43" s="15" t="inlineStr"/>
-      <c r="AQ43" s="15" t="inlineStr"/>
-      <c r="AR43" s="15" t="inlineStr"/>
-      <c r="AS43" s="15" t="inlineStr"/>
-      <c r="AT43" s="15" t="inlineStr"/>
-      <c r="AU43" s="15" t="inlineStr"/>
-      <c r="AV43" s="15" t="inlineStr"/>
-      <c r="AW43" s="15" t="inlineStr"/>
-      <c r="AX43" s="15" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>secret-riso-club</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Secret Riso Club</t>
         </is>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E44" s="15" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>122 Central Ave, Brooklyn, NY</t>
         </is>
       </c>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Bushwick</t>
         </is>
       </c>
-      <c r="G44" s="15" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H44" s="15" t="n">
+      <c r="H44" t="n">
         <v>40.6985</v>
       </c>
-      <c r="I44" s="15" t="n">
+      <c r="I44" t="n">
         <v>-73.9298</v>
       </c>
-      <c r="J44" s="15" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K44" s="15" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L44" s="15" t="inlineStr"/>
-      <c r="M44" s="15" t="inlineStr"/>
-      <c r="N44" s="15" t="inlineStr"/>
-      <c r="O44" s="15" t="inlineStr"/>
-      <c r="P44" s="15" t="inlineStr"/>
-      <c r="Q44" s="15" t="inlineStr"/>
-      <c r="R44" s="15" t="inlineStr"/>
-      <c r="S44" s="15" t="inlineStr"/>
-      <c r="T44" s="15" t="inlineStr"/>
-      <c r="U44" s="15" t="inlineStr"/>
-      <c r="V44" s="15" t="inlineStr"/>
-      <c r="W44" s="15" t="inlineStr"/>
-      <c r="X44" s="15" t="inlineStr"/>
-      <c r="Y44" s="15" t="inlineStr"/>
-      <c r="Z44" s="15" t="inlineStr"/>
-      <c r="AA44" s="15" t="inlineStr"/>
-      <c r="AB44" s="15" t="inlineStr"/>
-      <c r="AC44" s="15" t="inlineStr"/>
-      <c r="AD44" s="15" t="inlineStr"/>
-      <c r="AE44" s="15" t="inlineStr"/>
-      <c r="AF44" s="15" t="inlineStr"/>
-      <c r="AG44" s="15" t="inlineStr"/>
-      <c r="AH44" s="15" t="inlineStr"/>
-      <c r="AI44" s="15" t="inlineStr"/>
-      <c r="AJ44" s="15" t="inlineStr"/>
-      <c r="AK44" s="15" t="inlineStr"/>
-      <c r="AL44" s="15" t="inlineStr"/>
-      <c r="AM44" s="15" t="inlineStr"/>
-      <c r="AN44" s="15" t="inlineStr"/>
-      <c r="AO44" s="15" t="inlineStr"/>
-      <c r="AP44" s="15" t="inlineStr"/>
-      <c r="AQ44" s="15" t="inlineStr"/>
-      <c r="AR44" s="15" t="inlineStr"/>
-      <c r="AS44" s="15" t="inlineStr"/>
-      <c r="AT44" s="15" t="inlineStr"/>
-      <c r="AU44" s="15" t="inlineStr"/>
-      <c r="AV44" s="15" t="inlineStr"/>
-      <c r="AW44" s="15" t="inlineStr"/>
-      <c r="AX44" s="15" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>brooklyn-brewery</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Brooklyn Brewery</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Bar / cafe / restaurant</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr"/>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Williamsburg</t>
         </is>
       </c>
-      <c r="G45" s="15" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H45" s="15" t="n">
+      <c r="H45" t="n">
         <v>40.7216</v>
       </c>
-      <c r="I45" s="15" t="n">
+      <c r="I45" t="n">
         <v>-73.9573</v>
       </c>
-      <c r="J45" s="15" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K45" s="15" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L45" s="15" t="inlineStr"/>
-      <c r="M45" s="15" t="inlineStr"/>
-      <c r="N45" s="15" t="inlineStr"/>
-      <c r="O45" s="15" t="inlineStr"/>
-      <c r="P45" s="15" t="inlineStr"/>
-      <c r="Q45" s="15" t="inlineStr"/>
-      <c r="R45" s="15" t="inlineStr"/>
-      <c r="S45" s="15" t="inlineStr"/>
-      <c r="T45" s="15" t="inlineStr"/>
-      <c r="U45" s="15" t="inlineStr"/>
-      <c r="V45" s="15" t="inlineStr"/>
-      <c r="W45" s="15" t="inlineStr"/>
-      <c r="X45" s="15" t="inlineStr"/>
-      <c r="Y45" s="15" t="inlineStr"/>
-      <c r="Z45" s="15" t="inlineStr"/>
-      <c r="AA45" s="15" t="inlineStr"/>
-      <c r="AB45" s="15" t="inlineStr"/>
-      <c r="AC45" s="15" t="inlineStr"/>
-      <c r="AD45" s="15" t="inlineStr"/>
-      <c r="AE45" s="15" t="inlineStr"/>
-      <c r="AF45" s="15" t="inlineStr"/>
-      <c r="AG45" s="15" t="inlineStr"/>
-      <c r="AH45" s="15" t="inlineStr"/>
-      <c r="AI45" s="15" t="inlineStr"/>
-      <c r="AJ45" s="15" t="inlineStr"/>
-      <c r="AK45" s="15" t="inlineStr"/>
-      <c r="AL45" s="15" t="inlineStr"/>
-      <c r="AM45" s="15" t="inlineStr"/>
-      <c r="AN45" s="15" t="inlineStr"/>
-      <c r="AO45" s="15" t="inlineStr"/>
-      <c r="AP45" s="15" t="inlineStr"/>
-      <c r="AQ45" s="15" t="inlineStr"/>
-      <c r="AR45" s="15" t="inlineStr"/>
-      <c r="AS45" s="15" t="inlineStr"/>
-      <c r="AT45" s="15" t="inlineStr"/>
-      <c r="AU45" s="15" t="inlineStr"/>
-      <c r="AV45" s="15" t="inlineStr"/>
-      <c r="AW45" s="15" t="inlineStr"/>
-      <c r="AX45" s="15" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>caveat</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Caveat</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Club / event venue</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr"/>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Lower East Side</t>
         </is>
       </c>
-      <c r="G46" s="15" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H46" s="15" t="n">
+      <c r="H46" t="n">
         <v>40.7208</v>
       </c>
-      <c r="I46" s="15" t="n">
+      <c r="I46" t="n">
         <v>-73.9842</v>
       </c>
-      <c r="J46" s="15" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K46" s="15" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L46" s="15" t="inlineStr"/>
-      <c r="M46" s="15" t="inlineStr"/>
-      <c r="N46" s="15" t="inlineStr"/>
-      <c r="O46" s="15" t="inlineStr"/>
-      <c r="P46" s="15" t="inlineStr"/>
-      <c r="Q46" s="15" t="inlineStr"/>
-      <c r="R46" s="15" t="inlineStr"/>
-      <c r="S46" s="15" t="inlineStr"/>
-      <c r="T46" s="15" t="inlineStr"/>
-      <c r="U46" s="15" t="inlineStr"/>
-      <c r="V46" s="15" t="inlineStr"/>
-      <c r="W46" s="15" t="inlineStr"/>
-      <c r="X46" s="15" t="inlineStr"/>
-      <c r="Y46" s="15" t="inlineStr"/>
-      <c r="Z46" s="15" t="inlineStr"/>
-      <c r="AA46" s="15" t="inlineStr"/>
-      <c r="AB46" s="15" t="inlineStr"/>
-      <c r="AC46" s="15" t="inlineStr"/>
-      <c r="AD46" s="15" t="inlineStr"/>
-      <c r="AE46" s="15" t="inlineStr"/>
-      <c r="AF46" s="15" t="inlineStr"/>
-      <c r="AG46" s="15" t="inlineStr"/>
-      <c r="AH46" s="15" t="inlineStr"/>
-      <c r="AI46" s="15" t="inlineStr"/>
-      <c r="AJ46" s="15" t="inlineStr"/>
-      <c r="AK46" s="15" t="inlineStr"/>
-      <c r="AL46" s="15" t="inlineStr"/>
-      <c r="AM46" s="15" t="inlineStr"/>
-      <c r="AN46" s="15" t="inlineStr"/>
-      <c r="AO46" s="15" t="inlineStr"/>
-      <c r="AP46" s="15" t="inlineStr"/>
-      <c r="AQ46" s="15" t="inlineStr"/>
-      <c r="AR46" s="15" t="inlineStr"/>
-      <c r="AS46" s="15" t="inlineStr"/>
-      <c r="AT46" s="15" t="inlineStr"/>
-      <c r="AU46" s="15" t="inlineStr"/>
-      <c r="AV46" s="15" t="inlineStr"/>
-      <c r="AW46" s="15" t="inlineStr"/>
-      <c r="AX46" s="15" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>520-8th-ave-3rd-fl</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>520 8th Ave., 3rd Fl. (CDNY)</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>520 8th Ave, 3rd Fl, New York, NY 10018</t>
         </is>
       </c>
-      <c r="F47" s="15" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Midtown</t>
         </is>
       </c>
-      <c r="G47" s="15" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H47" s="15" t="n">
+      <c r="H47" t="n">
         <v>40.7536</v>
       </c>
-      <c r="I47" s="15" t="n">
+      <c r="I47" t="n">
         <v>-73.994</v>
       </c>
-      <c r="J47" s="15" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K47" s="15" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L47" s="15" t="inlineStr"/>
-      <c r="M47" s="15" t="inlineStr"/>
-      <c r="N47" s="15" t="inlineStr"/>
-      <c r="O47" s="15" t="inlineStr"/>
-      <c r="P47" s="15" t="inlineStr"/>
-      <c r="Q47" s="15" t="inlineStr"/>
-      <c r="R47" s="15" t="inlineStr"/>
-      <c r="S47" s="15" t="inlineStr"/>
-      <c r="T47" s="15" t="inlineStr"/>
-      <c r="U47" s="15" t="inlineStr"/>
-      <c r="V47" s="15" t="inlineStr"/>
-      <c r="W47" s="15" t="inlineStr"/>
-      <c r="X47" s="15" t="inlineStr"/>
-      <c r="Y47" s="15" t="inlineStr"/>
-      <c r="Z47" s="15" t="inlineStr"/>
-      <c r="AA47" s="15" t="inlineStr"/>
-      <c r="AB47" s="15" t="inlineStr"/>
-      <c r="AC47" s="15" t="inlineStr"/>
-      <c r="AD47" s="15" t="inlineStr"/>
-      <c r="AE47" s="15" t="inlineStr"/>
-      <c r="AF47" s="15" t="inlineStr"/>
-      <c r="AG47" s="15" t="inlineStr"/>
-      <c r="AH47" s="15" t="inlineStr"/>
-      <c r="AI47" s="15" t="inlineStr"/>
-      <c r="AJ47" s="15" t="inlineStr"/>
-      <c r="AK47" s="15" t="inlineStr"/>
-      <c r="AL47" s="15" t="inlineStr"/>
-      <c r="AM47" s="15" t="inlineStr"/>
-      <c r="AN47" s="15" t="inlineStr"/>
-      <c r="AO47" s="15" t="inlineStr"/>
-      <c r="AP47" s="15" t="inlineStr"/>
-      <c r="AQ47" s="15" t="inlineStr"/>
-      <c r="AR47" s="15" t="inlineStr"/>
-      <c r="AS47" s="15" t="inlineStr"/>
-      <c r="AT47" s="15" t="inlineStr"/>
-      <c r="AU47" s="15" t="inlineStr"/>
-      <c r="AV47" s="15" t="inlineStr"/>
-      <c r="AW47" s="15" t="inlineStr"/>
-      <c r="AX47" s="15" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>maria-hernandez-park</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Maria Hernandez Park</t>
         </is>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr"/>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Bushwick</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H48" s="15" t="n">
+      <c r="H48" t="n">
         <v>40.703</v>
       </c>
-      <c r="I48" s="15" t="n">
+      <c r="I48" t="n">
         <v>-73.9235</v>
       </c>
-      <c r="J48" s="15" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K48" s="15" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L48" s="15" t="inlineStr"/>
-      <c r="M48" s="15" t="inlineStr"/>
-      <c r="N48" s="15" t="inlineStr"/>
-      <c r="O48" s="15" t="inlineStr"/>
-      <c r="P48" s="15" t="inlineStr"/>
-      <c r="Q48" s="15" t="inlineStr"/>
-      <c r="R48" s="15" t="inlineStr"/>
-      <c r="S48" s="15" t="inlineStr"/>
-      <c r="T48" s="15" t="inlineStr"/>
-      <c r="U48" s="15" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V48" s="15" t="inlineStr"/>
-      <c r="W48" s="15" t="inlineStr"/>
-      <c r="X48" s="15" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y48" s="15" t="inlineStr"/>
-      <c r="Z48" s="15" t="inlineStr"/>
-      <c r="AA48" s="15" t="inlineStr"/>
-      <c r="AB48" s="15" t="inlineStr"/>
-      <c r="AC48" s="15" t="inlineStr"/>
-      <c r="AD48" s="15" t="inlineStr"/>
-      <c r="AE48" s="15" t="inlineStr"/>
-      <c r="AF48" s="15" t="inlineStr"/>
-      <c r="AG48" s="15" t="inlineStr"/>
-      <c r="AH48" s="15" t="inlineStr"/>
-      <c r="AI48" s="15" t="inlineStr"/>
-      <c r="AJ48" s="15" t="inlineStr"/>
-      <c r="AK48" s="15" t="inlineStr"/>
-      <c r="AL48" s="15" t="inlineStr"/>
-      <c r="AM48" s="15" t="inlineStr"/>
-      <c r="AN48" s="15" t="inlineStr"/>
-      <c r="AO48" s="15" t="inlineStr"/>
-      <c r="AP48" s="15" t="inlineStr"/>
-      <c r="AQ48" s="15" t="inlineStr"/>
-      <c r="AR48" s="15" t="inlineStr"/>
-      <c r="AS48" s="15" t="inlineStr"/>
-      <c r="AT48" s="15" t="inlineStr"/>
-      <c r="AU48" s="15" t="inlineStr"/>
-      <c r="AV48" s="15" t="inlineStr"/>
-      <c r="AW48" s="15" t="inlineStr"/>
-      <c r="AX48" s="15" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>newtown-radio</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Newtown Radio</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Radio station / studio</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>262 Meserole St, Brooklyn, NY</t>
         </is>
       </c>
-      <c r="F49" s="15" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>East Williamsburg</t>
         </is>
       </c>
-      <c r="G49" s="15" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H49" s="15" t="n">
+      <c r="H49" t="n">
         <v>40.7079</v>
       </c>
-      <c r="I49" s="15" t="n">
+      <c r="I49" t="n">
         <v>-73.93300000000001</v>
       </c>
-      <c r="J49" s="15" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K49" s="15" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L49" s="15" t="inlineStr"/>
-      <c r="M49" s="15" t="inlineStr"/>
-      <c r="N49" s="15" t="inlineStr"/>
-      <c r="O49" s="15" t="inlineStr"/>
-      <c r="P49" s="15" t="inlineStr"/>
-      <c r="Q49" s="15" t="inlineStr"/>
-      <c r="R49" s="15" t="inlineStr"/>
-      <c r="S49" s="15" t="inlineStr"/>
-      <c r="T49" s="15" t="inlineStr"/>
-      <c r="U49" s="15" t="inlineStr"/>
-      <c r="V49" s="15" t="inlineStr"/>
-      <c r="W49" s="15" t="inlineStr"/>
-      <c r="X49" s="15" t="inlineStr"/>
-      <c r="Y49" s="15" t="inlineStr"/>
-      <c r="Z49" s="15" t="inlineStr"/>
-      <c r="AA49" s="15" t="inlineStr"/>
-      <c r="AB49" s="15" t="inlineStr"/>
-      <c r="AC49" s="15" t="inlineStr"/>
-      <c r="AD49" s="15" t="inlineStr"/>
-      <c r="AE49" s="15" t="inlineStr"/>
-      <c r="AF49" s="15" t="inlineStr"/>
-      <c r="AG49" s="15" t="inlineStr"/>
-      <c r="AH49" s="15" t="inlineStr"/>
-      <c r="AI49" s="15" t="inlineStr"/>
-      <c r="AJ49" s="15" t="inlineStr"/>
-      <c r="AK49" s="15" t="inlineStr"/>
-      <c r="AL49" s="15" t="inlineStr"/>
-      <c r="AM49" s="15" t="inlineStr"/>
-      <c r="AN49" s="15" t="inlineStr"/>
-      <c r="AO49" s="15" t="inlineStr"/>
-      <c r="AP49" s="15" t="inlineStr"/>
-      <c r="AQ49" s="15" t="inlineStr"/>
-      <c r="AR49" s="15" t="inlineStr"/>
-      <c r="AS49" s="15" t="inlineStr"/>
-      <c r="AT49" s="15" t="inlineStr"/>
-      <c r="AU49" s="15" t="inlineStr"/>
-      <c r="AV49" s="15" t="inlineStr"/>
-      <c r="AW49" s="15" t="inlineStr"/>
-      <c r="AX49" s="15" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>pioneer-works</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Pioneer Works</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Arts / community space</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr"/>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Red Hook</t>
         </is>
       </c>
-      <c r="G50" s="15" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H50" s="15" t="n">
+      <c r="H50" t="n">
         <v>40.6788</v>
       </c>
-      <c r="I50" s="15" t="n">
+      <c r="I50" t="n">
         <v>-74.012</v>
       </c>
-      <c r="J50" s="15" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K50" s="15" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L50" s="15" t="inlineStr"/>
-      <c r="M50" s="15" t="inlineStr"/>
-      <c r="N50" s="15" t="inlineStr"/>
-      <c r="O50" s="15" t="inlineStr"/>
-      <c r="P50" s="15" t="inlineStr"/>
-      <c r="Q50" s="15" t="inlineStr"/>
-      <c r="R50" s="15" t="inlineStr"/>
-      <c r="S50" s="15" t="inlineStr"/>
-      <c r="T50" s="15" t="inlineStr"/>
-      <c r="U50" s="15" t="inlineStr"/>
-      <c r="V50" s="15" t="inlineStr"/>
-      <c r="W50" s="15" t="inlineStr"/>
-      <c r="X50" s="15" t="inlineStr"/>
-      <c r="Y50" s="15" t="inlineStr"/>
-      <c r="Z50" s="15" t="inlineStr"/>
-      <c r="AA50" s="15" t="inlineStr"/>
-      <c r="AB50" s="15" t="inlineStr"/>
-      <c r="AC50" s="15" t="inlineStr"/>
-      <c r="AD50" s="15" t="inlineStr"/>
-      <c r="AE50" s="15" t="inlineStr"/>
-      <c r="AF50" s="15" t="inlineStr"/>
-      <c r="AG50" s="15" t="inlineStr"/>
-      <c r="AH50" s="15" t="inlineStr"/>
-      <c r="AI50" s="15" t="inlineStr"/>
-      <c r="AJ50" s="15" t="inlineStr"/>
-      <c r="AK50" s="15" t="inlineStr"/>
-      <c r="AL50" s="15" t="inlineStr"/>
-      <c r="AM50" s="15" t="inlineStr"/>
-      <c r="AN50" s="15" t="inlineStr"/>
-      <c r="AO50" s="15" t="inlineStr"/>
-      <c r="AP50" s="15" t="inlineStr"/>
-      <c r="AQ50" s="15" t="inlineStr"/>
-      <c r="AR50" s="15" t="inlineStr"/>
-      <c r="AS50" s="15" t="inlineStr"/>
-      <c r="AT50" s="15" t="inlineStr"/>
-      <c r="AU50" s="15" t="inlineStr"/>
-      <c r="AV50" s="15" t="inlineStr"/>
-      <c r="AW50" s="15" t="inlineStr"/>
-      <c r="AX50" s="15" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>tane-poetry-library</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C51" s="15" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Tane Poetry Library</t>
         </is>
       </c>
-      <c r="D51" s="15" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="E51" s="15" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>91 South St, New York, NY</t>
         </is>
       </c>
-      <c r="F51" s="15" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>South Street Seaport</t>
         </is>
       </c>
-      <c r="G51" s="15" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H51" s="15" t="n">
+      <c r="H51" t="n">
         <v>40.7063</v>
       </c>
-      <c r="I51" s="15" t="n">
+      <c r="I51" t="n">
         <v>-74.0033</v>
       </c>
-      <c r="J51" s="15" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K51" s="15" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L51" s="15" t="inlineStr"/>
-      <c r="M51" s="15" t="inlineStr"/>
-      <c r="N51" s="15" t="inlineStr"/>
-      <c r="O51" s="15" t="inlineStr"/>
-      <c r="P51" s="15" t="inlineStr"/>
-      <c r="Q51" s="15" t="inlineStr"/>
-      <c r="R51" s="15" t="inlineStr"/>
-      <c r="S51" s="15" t="inlineStr"/>
-      <c r="T51" s="15" t="inlineStr"/>
-      <c r="U51" s="15" t="inlineStr"/>
-      <c r="V51" s="15" t="inlineStr"/>
-      <c r="W51" s="15" t="inlineStr"/>
-      <c r="X51" s="15" t="inlineStr"/>
-      <c r="Y51" s="15" t="inlineStr"/>
-      <c r="Z51" s="15" t="inlineStr"/>
-      <c r="AA51" s="15" t="inlineStr"/>
-      <c r="AB51" s="15" t="inlineStr"/>
-      <c r="AC51" s="15" t="inlineStr"/>
-      <c r="AD51" s="15" t="inlineStr"/>
-      <c r="AE51" s="15" t="inlineStr"/>
-      <c r="AF51" s="15" t="inlineStr"/>
-      <c r="AG51" s="15" t="inlineStr"/>
-      <c r="AH51" s="15" t="inlineStr"/>
-      <c r="AI51" s="15" t="inlineStr"/>
-      <c r="AJ51" s="15" t="inlineStr"/>
-      <c r="AK51" s="15" t="inlineStr"/>
-      <c r="AL51" s="15" t="inlineStr"/>
-      <c r="AM51" s="15" t="inlineStr"/>
-      <c r="AN51" s="15" t="inlineStr"/>
-      <c r="AO51" s="15" t="inlineStr"/>
-      <c r="AP51" s="15" t="inlineStr"/>
-      <c r="AQ51" s="15" t="inlineStr"/>
-      <c r="AR51" s="15" t="inlineStr"/>
-      <c r="AS51" s="15" t="inlineStr"/>
-      <c r="AT51" s="15" t="inlineStr"/>
-      <c r="AU51" s="15" t="inlineStr"/>
-      <c r="AV51" s="15" t="inlineStr"/>
-      <c r="AW51" s="15" t="inlineStr"/>
-      <c r="AX51" s="15" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>177-prince-st</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>177 Prince St. (Museum of Interesting Things)</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Gallery / museum</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>177 Prince St, New York, NY 10012</t>
         </is>
       </c>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>SoHo</t>
         </is>
       </c>
-      <c r="G52" s="15" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Manhattan</t>
         </is>
       </c>
-      <c r="H52" s="15" t="n">
+      <c r="H52" t="n">
         <v>40.7263</v>
       </c>
-      <c r="I52" s="15" t="n">
+      <c r="I52" t="n">
         <v>-74.0018</v>
       </c>
-      <c r="J52" s="15" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K52" s="15" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Indoor</t>
         </is>
       </c>
-      <c r="L52" s="15" t="inlineStr"/>
-      <c r="M52" s="15" t="inlineStr"/>
-      <c r="N52" s="15" t="inlineStr"/>
-      <c r="O52" s="15" t="inlineStr"/>
-      <c r="P52" s="15" t="inlineStr"/>
-      <c r="Q52" s="15" t="inlineStr"/>
-      <c r="R52" s="15" t="inlineStr"/>
-      <c r="S52" s="15" t="inlineStr"/>
-      <c r="T52" s="15" t="inlineStr"/>
-      <c r="U52" s="15" t="inlineStr"/>
-      <c r="V52" s="15" t="inlineStr"/>
-      <c r="W52" s="15" t="inlineStr"/>
-      <c r="X52" s="15" t="inlineStr"/>
-      <c r="Y52" s="15" t="inlineStr"/>
-      <c r="Z52" s="15" t="inlineStr"/>
-      <c r="AA52" s="15" t="inlineStr"/>
-      <c r="AB52" s="15" t="inlineStr"/>
-      <c r="AC52" s="15" t="inlineStr"/>
-      <c r="AD52" s="15" t="inlineStr"/>
-      <c r="AE52" s="15" t="inlineStr"/>
-      <c r="AF52" s="15" t="inlineStr"/>
-      <c r="AG52" s="15" t="inlineStr"/>
-      <c r="AH52" s="15" t="inlineStr"/>
-      <c r="AI52" s="15" t="inlineStr"/>
-      <c r="AJ52" s="15" t="inlineStr"/>
-      <c r="AK52" s="15" t="inlineStr"/>
-      <c r="AL52" s="15" t="inlineStr"/>
-      <c r="AM52" s="15" t="inlineStr"/>
-      <c r="AN52" s="15" t="inlineStr"/>
-      <c r="AO52" s="15" t="inlineStr"/>
-      <c r="AP52" s="15" t="inlineStr"/>
-      <c r="AQ52" s="15" t="inlineStr"/>
-      <c r="AR52" s="15" t="inlineStr"/>
-      <c r="AS52" s="15" t="inlineStr"/>
-      <c r="AT52" s="15" t="inlineStr"/>
-      <c r="AU52" s="15" t="inlineStr"/>
-      <c r="AV52" s="15" t="inlineStr"/>
-      <c r="AW52" s="15" t="inlineStr"/>
-      <c r="AX52" s="15" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>mccarren-park</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>McCarren Park</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Park / public space</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr"/>
-      <c r="F53" s="15" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Williamsburg/Greenpoint</t>
         </is>
       </c>
-      <c r="G53" s="15" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Brooklyn</t>
         </is>
       </c>
-      <c r="H53" s="15" t="n">
+      <c r="H53" t="n">
         <v>40.7206</v>
       </c>
-      <c r="I53" s="15" t="n">
+      <c r="I53" t="n">
         <v>-73.9516</v>
       </c>
-      <c r="J53" s="15" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="K53" s="15" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Outdoor</t>
         </is>
       </c>
-      <c r="L53" s="15" t="inlineStr"/>
-      <c r="M53" s="15" t="inlineStr"/>
-      <c r="N53" s="15" t="inlineStr"/>
-      <c r="O53" s="15" t="inlineStr"/>
-      <c r="P53" s="15" t="inlineStr"/>
-      <c r="Q53" s="15" t="inlineStr"/>
-      <c r="R53" s="15" t="inlineStr"/>
-      <c r="S53" s="15" t="inlineStr"/>
-      <c r="T53" s="15" t="inlineStr"/>
-      <c r="U53" s="15" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="V53" s="15" t="inlineStr"/>
-      <c r="W53" s="15" t="inlineStr"/>
-      <c r="X53" s="15" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Public park: check NYC Parks special event permit rules for larger groups, tables or structures, and NYPD sound permit for amplified sound.</t>
         </is>
       </c>
-      <c r="Y53" s="15" t="inlineStr"/>
-      <c r="Z53" s="15" t="inlineStr"/>
-      <c r="AA53" s="15" t="inlineStr"/>
-      <c r="AB53" s="15" t="inlineStr"/>
-      <c r="AC53" s="15" t="inlineStr"/>
-      <c r="AD53" s="15" t="inlineStr"/>
-      <c r="AE53" s="15" t="inlineStr"/>
-      <c r="AF53" s="15" t="inlineStr"/>
-      <c r="AG53" s="15" t="inlineStr"/>
-      <c r="AH53" s="15" t="inlineStr"/>
-      <c r="AI53" s="15" t="inlineStr"/>
-      <c r="AJ53" s="15" t="inlineStr"/>
-      <c r="AK53" s="15" t="inlineStr"/>
-      <c r="AL53" s="15" t="inlineStr"/>
-      <c r="AM53" s="15" t="inlineStr"/>
-      <c r="AN53" s="15" t="inlineStr"/>
-      <c r="AO53" s="15" t="inlineStr"/>
-      <c r="AP53" s="15" t="inlineStr"/>
-      <c r="AQ53" s="15" t="inlineStr"/>
-      <c r="AR53" s="15" t="inlineStr"/>
-      <c r="AS53" s="15" t="inlineStr"/>
-      <c r="AT53" s="15" t="inlineStr"/>
-      <c r="AU53" s="15" t="inlineStr"/>
-      <c r="AV53" s="15" t="inlineStr"/>
-      <c r="AW53" s="15" t="inlineStr"/>
-      <c r="AX53" s="15" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>Initial research (NYC Off Tech newsletter)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AX53"/>
-  <dataValidations count="23">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Approved,Pending review,Archived"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Park / public space,Privately owned public space (POPS),Library,Bar / cafe / restaurant,Club / event venue,Arts / community space,Gallery / museum,Bookstore,Church / meeting house,University,Makerspace,Community tech space,Radio station / studio,Other"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Manhattan,Brooklyn,Queens,Bronx,Staten Island"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"exact,approx"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Indoor,Outdoor,Both"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"None,Some,Plenty,Bring your own"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No,Some"</formula1>
-    </dataValidation>
-    <dataValidation sqref="P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No,Ask"</formula1>
-    </dataValidation>
-    <dataValidation sqref="R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Quiet,Conversational,Loud"</formula1>
-    </dataValidation>
-    <dataValidation sqref="S2:S500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No,With permit,Ask"</formula1>
-    </dataValidation>
-    <dataValidation sqref="T2:T500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No,Ask"</formula1>
-    </dataValidation>
-    <dataValidation sqref="U2:U500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Free,Donation,Purchase / minimum spend,Rental fee,Ticketed by venue,Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="W2:W500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Just show up,Ask staff in person,Email,Online form,Permit required,Through an organizer"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AA2:AA500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Outside food OK,Purchase required,No food or drink,Ask"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AB2:AB500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Served,BYO allowed,Not allowed,Ask"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AC2:AC500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,21+,18+,Ask"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AD2:AD500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No,Nearby"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AE2:AE500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No,Partial,Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AF2:AF500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No,Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AH2:AH500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No,Limited"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AI2:AI500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No,Ask"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AJ2:AJ500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No,Ask"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AS2:AS500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -24644,7 +22394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -24682,1182 +22432,582 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Venue ID</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D2" s="19" t="inlineStr"/>
-      <c r="E2" s="19" t="inlineStr">
-        <is>
-          <t>Stable ID used as the URL slug. Don't change once set; leave blank for new venues and the sync script will create one.</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stable ID used as the URL slug. Don't change once set; leave blank for new venues and the sync will create one.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Approved · Pending review · Archived</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Only Approved venues appear on the site. New venues start as Pending review.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Venue name</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr"/>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Common name of the space.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Venue type</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Park / public space · Privately owned public space (POPS) · Library · Bar / cafe / restaurant · Club / event venue · Arts / community space · Gallery / museum · Bookstore · Church / meeting house · University · Makerspace · Community tech space · Radio station / studio · Other</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>What kind of place this is.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Street address</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Full street address. Public business or institutional addresses only. Never a private home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Neighborhood</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Borough</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Manhattan · Brooklyn · Queens · Bronx · Staten Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr"/>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>Full street address. Public business or institutional addresses only. Never a private home.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>Neighborhood</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Decimal degrees. The sync can fill this from the address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr"/>
-      <c r="E7" s="19" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>Borough</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Decimal degrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Location precision</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>Manhattan · Brooklyn · Queens · Bronx · Staten Island</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>exact · approx</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>approx = pin placed by neighborhood or cross street; confirm the address to upgrade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Indoor / outdoor</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>Decimal degrees. The sync script can fill this from the address.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Indoor · Outdoor · Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Capacity (est.)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>Decimal degrees.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>Location precision</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Rough number of people the space holds. An estimate is fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Venue details</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>exact · approx</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>approx = pin placed by neighborhood or cross street; confirm the address to upgrade.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Indoor / outdoor</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Free · Donation · Purchase / minimum spend · Rental fee · Ticketed by venue · Unknown</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Shown as 'Public / cost'. Parks, plazas and libraries also show as public spaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>How to book</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>Indoor · Outdoor · Both</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>Capacity, standing (est.)</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Freeform. Who to ask, how far ahead, permits, any fees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr"/>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>Rough number of people standing. An estimate is fine; say so in notes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>Capacity, seated (est.)</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Freeform and PUBLIC: a venue's events email, booking form or front desk. Never a personal email or phone; those go in the collaborator-only columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Food &amp; drink</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr"/>
-      <c r="E14" s="19" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>Seating</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Freeform. Outside food OK? Purchase required? Alcohol?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>None · Some · Plenty · Bring your own</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>Is there somewhere for people to sit?</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>Tables available</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Freeform. Step-free entry, elevator, accessible restroom, seating, lighting, quiet corner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A/V equipment</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No · Some</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Useful for crafts, zines and letter writing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>Private room / buyout</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Freeform. Power outlets, sound system or mic, projector or screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Other notes</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Venue notes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No · Ask</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>Can a group have its own room or the whole venue?</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>Weather backup</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Freeform. Anything else: where to set up, what's worked, what to avoid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Key contact</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Collaborators only</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Collaborators only</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Who to talk to about events, and their role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Contact email</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Collaborators only</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Collaborators only</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Prefer a business or events address over a personal one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Contact phone</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Collaborators only</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Collaborators only</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Business line only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Relationship notes</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Collaborators only</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Collaborators only</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Who in the community knows them, past events, any history to be aware of.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Last verified</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Upkeep</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr"/>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>Outdoor venues: nearest indoor fallback, or how hosts have handled rain.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>Noise level</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>Atmosphere</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>Quiet · Conversational · Loud</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>Can people talk and hear each other?</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>Amplified sound allowed</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>Atmosphere</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No · With permit · Ask</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>Phone-free friendly</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>Atmosphere</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No · Ask</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>Has the venue been OK with phone-free rules, phone check or lockers?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>Free · Donation · Purchase / minimum spend · Rental fee · Ticketed by venue · Unknown</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>Cost notes</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr"/>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>e.g. '$X minimum on weeknights', 'free for community groups'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>How to book</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>Just show up · Ask staff in person · Email · Online form · Permit required · Through an organizer</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>How hosts have secured the space.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>Permit notes</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr"/>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>Parks and plazas: permits needed for larger groups, amplified sound, tables or structures. Check NYC Parks and NYPD rules.</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Date someone last confirmed these details (YYYY-MM-DD).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>Booking lead time</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr"/>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>e.g. 'same week', '4+ weeks'.</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Verified by</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Upkeep</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>Hours / best times</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr"/>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>When events work here: weeknights, weekend afternoons, etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>Food &amp; drink</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>Amenities</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>Outside food OK · Purchase required · No food or drink · Ask</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>Alcohol</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>Amenities</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>Served · BYO allowed · Not allowed · Ask</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>All ages</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>Amenities</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>Yes · 21+ · 18+ · Ask</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>Restrooms</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>Amenities</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No · Nearby</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>Step-free access</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No · Partial · Unknown</t>
-        </is>
-      </c>
-      <c r="E32" s="19" t="inlineStr">
-        <is>
-          <t>Can a wheelchair user get in without stairs?</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>Accessible restroom</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No · Unknown</t>
-        </is>
-      </c>
-      <c r="E33" s="19" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>Accessibility notes</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr"/>
-      <c r="E34" s="19" t="inlineStr">
-        <is>
-          <t>Elevator, ramp, lighting, seating with backs, quiet corner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>Power outlets</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No · Limited</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="inlineStr">
-        <is>
-          <t>For a record player, projector or soldering irons.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>Sound system / mic</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No · Ask</t>
-        </is>
-      </c>
-      <c r="E36" s="19" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>Projector / screen</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No · Ask</t>
-        </is>
-      </c>
-      <c r="E37" s="19" t="inlineStr">
-        <is>
-          <t>For screenings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>Nearest transit</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>Getting there</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr"/>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>Subway lines and stop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>Links</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr"/>
-      <c r="E39" s="19" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>Links</t>
-        </is>
-      </c>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="inlineStr"/>
-      <c r="E40" s="19" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>Public booking / inquiry link</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>Links</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr"/>
-      <c r="E41" s="19" t="inlineStr">
-        <is>
-          <t>A venue's own public form or events email page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>Key contact</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>Collaborators only</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr"/>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>Who to talk to about events (role is fine if no name).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>Contact role</t>
-        </is>
-      </c>
-      <c r="B43" s="19" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="C43" s="19" t="inlineStr">
-        <is>
-          <t>Collaborators only</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr"/>
-      <c r="E43" s="19" t="inlineStr">
-        <is>
-          <t>e.g. owner, events manager, librarian.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>Contact email</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="inlineStr">
-        <is>
-          <t>Collaborators only</t>
-        </is>
-      </c>
-      <c r="D44" s="19" t="inlineStr"/>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>Prefer a business or events address over a personal one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>Contact phone</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>Collaborators only</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr"/>
-      <c r="E45" s="19" t="inlineStr">
-        <is>
-          <t>Business line only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="19" t="inlineStr">
-        <is>
-          <t>OK to show contact publicly?</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Submitted by</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Upkeep</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D46" s="19" t="inlineStr">
-        <is>
-          <t>Yes · No</t>
-        </is>
-      </c>
-      <c r="E46" s="19" t="inlineStr">
-        <is>
-          <t>Only Yes if the venue has agreed. Otherwise the site shows the public booking link only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="19" t="inlineStr">
-        <is>
-          <t>Relationship notes</t>
-        </is>
-      </c>
-      <c r="B47" s="19" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>Collaborators only</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="inlineStr"/>
-      <c r="E47" s="19" t="inlineStr">
-        <is>
-          <t>Who in the community knows them, past events, any history to be aware of.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="19" t="inlineStr">
-        <is>
-          <t>Notes for hosts</t>
-        </is>
-      </c>
-      <c r="B48" s="19" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D48" s="19" t="inlineStr"/>
-      <c r="E48" s="19" t="inlineStr">
-        <is>
-          <t>About the space, shown under 'Venue notes' on the venue page: where to set up, what's worked, what to avoid. Food &amp; drink, Alcohol and contact details (if the venue agreed) appear there too.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>Last verified</t>
-        </is>
-      </c>
-      <c r="B49" s="19" t="inlineStr">
-        <is>
-          <t>Upkeep</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr"/>
-      <c r="E49" s="19" t="inlineStr">
-        <is>
-          <t>Date someone last confirmed these details (YYYY-MM-DD).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="19" t="inlineStr">
-        <is>
-          <t>Verified by</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="inlineStr">
-        <is>
-          <t>Upkeep</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D50" s="19" t="inlineStr"/>
-      <c r="E50" s="19" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>Submitted by</t>
-        </is>
-      </c>
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t>Upkeep</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D51" s="19" t="inlineStr"/>
-      <c r="E51" s="19" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Who added the venue.</t>
         </is>

--- a/tools/find-a-venue/data/venues_master_seed.xlsx
+++ b/tools/find-a-venue/data/venues_master_seed.xlsx
@@ -3909,6 +3909,26 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="6">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Status" error="Pick one of: Approved, Pending review, Archived" type="list">
+      <formula1>"Approved,Pending review,Archived"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Venue type" error="Pick one of: Park / public space, Privately owned public space (POPS), Library, Bar / cafe / restaurant, Club / event venue, Arts / community space, Gallery / museum, Bookstore, Church / meeting house, University, Makerspace, Community tech space, Radio station / studio, Other" type="list">
+      <formula1>"Park / public space,Privately owned public space (POPS),Library,Bar / cafe / restaurant,Club / event venue,Arts / community space,Gallery / museum,Bookstore,Church / meeting house,University,Makerspace,Community tech space,Radio station / studio,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Borough" error="Pick one of: Manhattan, Brooklyn, Queens, Bronx, Staten Island" type="list">
+      <formula1>"Manhattan,Brooklyn,Queens,Bronx,Staten Island"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Location precision" error="Pick one of: exact, approx" type="list">
+      <formula1>"exact,approx"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Indoor / outdoor" error="Pick one of: Indoor, Outdoor, Both" type="list">
+      <formula1>"Indoor,Outdoor,Both"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Cost" error="Pick one of: Free, Donation, Purchase / minimum spend, Rental fee, Ticketed by venue, Unknown" type="list">
+      <formula1>"Free,Donation,Purchase / minimum spend,Rental fee,Ticketed by venue,Unknown"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
